--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 14 Sep 2026 21:56</t>
+          <t>Generated 15 Sep 2026 21:35</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5973,6 +5973,192 @@
         <v>1</v>
       </c>
       <c r="P85" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>99</v>
+      </c>
+      <c r="F86" t="n">
+        <v>126.43</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I86" t="n">
+        <v>16121</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="K86" t="n">
+        <v>18879</v>
+      </c>
+      <c r="L86" t="n">
+        <v>20258</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1379</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="O86" t="b">
+        <v>1</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>98</v>
+      </c>
+      <c r="F87" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>2676.6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2467.83</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2885.37</v>
+      </c>
+      <c r="L87" t="n">
+        <v>3094.14</v>
+      </c>
+      <c r="M87" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O87" t="b">
+        <v>1</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>96</v>
+      </c>
+      <c r="F88" t="n">
+        <v>105.41</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1969</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1871.34</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2066.66</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2164.32</v>
+      </c>
+      <c r="M88" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="O88" t="b">
+        <v>1</v>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -5989,7 +6175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8748,6 +8934,105 @@
         <v>2066.66</v>
       </c>
       <c r="I85" t="n">
+        <v>2164.32</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E86" t="n">
+        <v>16121</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1379</v>
+      </c>
+      <c r="H86" t="n">
+        <v>18879</v>
+      </c>
+      <c r="I86" t="n">
+        <v>20258</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2676.6</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2467.83</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2885.37</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3094.14</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1969</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1871.34</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="G88" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2066.66</v>
+      </c>
+      <c r="I88" t="n">
         <v>2164.32</v>
       </c>
     </row>
@@ -24752,7 +25037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25192,6 +25477,21 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 06 Oct 2026 00:13</t>
+          <t>Generated 06 Oct 2026 22:45</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
         <v>-0.66</v>
       </c>
       <c r="N109" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O109" t="n">
         <v>1251.99</v>
@@ -18959,7 +18959,7 @@
         <v>-1.9</v>
       </c>
       <c r="N110" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O110" t="n">
         <v>1318.08</v>
@@ -19444,7 +19444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G644"/>
+  <dimension ref="A1:G646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28883,34 +28883,34 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1554.3</v>
+        <v>2265</v>
       </c>
       <c r="D350" t="n">
-        <v>1569</v>
+        <v>2339.7</v>
       </c>
       <c r="E350" t="n">
-        <v>1551.3</v>
+        <v>2231.6</v>
       </c>
       <c r="F350" t="n">
-        <v>1557.6</v>
+        <v>2243.7</v>
       </c>
       <c r="G350" t="n">
-        <v>1001677</v>
+        <v>511911</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -28919,25 +28919,25 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1560.4</v>
+        <v>1554.3</v>
       </c>
       <c r="D351" t="n">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="E351" t="n">
-        <v>1520.4</v>
+        <v>1551.3</v>
       </c>
       <c r="F351" t="n">
-        <v>1529.8</v>
+        <v>1557.6</v>
       </c>
       <c r="G351" t="n">
-        <v>1011017</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -28946,25 +28946,25 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>1534.9</v>
+        <v>1560.4</v>
       </c>
       <c r="D352" t="n">
-        <v>1572.2</v>
+        <v>1561</v>
       </c>
       <c r="E352" t="n">
-        <v>1527.2</v>
+        <v>1520.4</v>
       </c>
       <c r="F352" t="n">
-        <v>1558.9</v>
+        <v>1529.8</v>
       </c>
       <c r="G352" t="n">
-        <v>1235837</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -28973,25 +28973,25 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1559.7</v>
+        <v>1534.9</v>
       </c>
       <c r="D353" t="n">
-        <v>1600.1</v>
+        <v>1572.2</v>
       </c>
       <c r="E353" t="n">
-        <v>1557</v>
+        <v>1527.2</v>
       </c>
       <c r="F353" t="n">
-        <v>1593.2</v>
+        <v>1558.9</v>
       </c>
       <c r="G353" t="n">
-        <v>1871739</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -29000,25 +29000,25 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>1591</v>
+        <v>1559.7</v>
       </c>
       <c r="D354" t="n">
+        <v>1600.1</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1557</v>
+      </c>
+      <c r="F354" t="n">
         <v>1593.2</v>
       </c>
-      <c r="E354" t="n">
-        <v>1566</v>
-      </c>
-      <c r="F354" t="n">
-        <v>1577.8</v>
-      </c>
       <c r="G354" t="n">
-        <v>1183077</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -29027,25 +29027,25 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>1577.7</v>
+        <v>1591</v>
       </c>
       <c r="D355" t="n">
-        <v>1586.1</v>
+        <v>1593.2</v>
       </c>
       <c r="E355" t="n">
-        <v>1561.1</v>
+        <v>1566</v>
       </c>
       <c r="F355" t="n">
-        <v>1568.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G355" t="n">
-        <v>1098268</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -29054,25 +29054,25 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1560</v>
+        <v>1577.7</v>
       </c>
       <c r="D356" t="n">
-        <v>1610</v>
+        <v>1586.1</v>
       </c>
       <c r="E356" t="n">
-        <v>1554.9</v>
+        <v>1561.1</v>
       </c>
       <c r="F356" t="n">
-        <v>1601.2</v>
+        <v>1568.3</v>
       </c>
       <c r="G356" t="n">
-        <v>2647403</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -29081,25 +29081,25 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1624.8</v>
+        <v>1560</v>
       </c>
       <c r="D357" t="n">
-        <v>1734.5</v>
+        <v>1610</v>
       </c>
       <c r="E357" t="n">
-        <v>1617.1</v>
+        <v>1554.9</v>
       </c>
       <c r="F357" t="n">
-        <v>1713.4</v>
+        <v>1601.2</v>
       </c>
       <c r="G357" t="n">
-        <v>7989771</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -29108,25 +29108,25 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1713</v>
+        <v>1624.8</v>
       </c>
       <c r="D358" t="n">
-        <v>1762</v>
+        <v>1734.5</v>
       </c>
       <c r="E358" t="n">
-        <v>1707.7</v>
+        <v>1617.1</v>
       </c>
       <c r="F358" t="n">
-        <v>1758.9</v>
+        <v>1713.4</v>
       </c>
       <c r="G358" t="n">
-        <v>4407907</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -29135,25 +29135,25 @@
         </is>
       </c>
       <c r="C359" t="n">
+        <v>1713</v>
+      </c>
+      <c r="D359" t="n">
         <v>1762</v>
       </c>
-      <c r="D359" t="n">
-        <v>1797.9</v>
-      </c>
       <c r="E359" t="n">
-        <v>1754.3</v>
+        <v>1707.7</v>
       </c>
       <c r="F359" t="n">
-        <v>1781.3</v>
+        <v>1758.9</v>
       </c>
       <c r="G359" t="n">
-        <v>3000811</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -29162,25 +29162,25 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>1785</v>
+        <v>1762</v>
       </c>
       <c r="D360" t="n">
-        <v>1798.9</v>
+        <v>1797.9</v>
       </c>
       <c r="E360" t="n">
-        <v>1773.3</v>
+        <v>1754.3</v>
       </c>
       <c r="F360" t="n">
         <v>1781.3</v>
       </c>
       <c r="G360" t="n">
-        <v>2402202</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -29192,22 +29192,22 @@
         <v>1785</v>
       </c>
       <c r="D361" t="n">
-        <v>1826.6</v>
+        <v>1798.9</v>
       </c>
       <c r="E361" t="n">
-        <v>1785</v>
+        <v>1773.3</v>
       </c>
       <c r="F361" t="n">
-        <v>1816.2</v>
+        <v>1781.3</v>
       </c>
       <c r="G361" t="n">
-        <v>2502579</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -29216,25 +29216,25 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1821</v>
+        <v>1785</v>
       </c>
       <c r="D362" t="n">
-        <v>1838.3</v>
+        <v>1826.6</v>
       </c>
       <c r="E362" t="n">
-        <v>1789.1</v>
+        <v>1785</v>
       </c>
       <c r="F362" t="n">
-        <v>1811.4</v>
+        <v>1816.2</v>
       </c>
       <c r="G362" t="n">
-        <v>1919384</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -29243,25 +29243,25 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>1811</v>
+        <v>1821</v>
       </c>
       <c r="D363" t="n">
-        <v>1850</v>
+        <v>1838.3</v>
       </c>
       <c r="E363" t="n">
-        <v>1806.1</v>
+        <v>1789.1</v>
       </c>
       <c r="F363" t="n">
-        <v>1850</v>
+        <v>1811.4</v>
       </c>
       <c r="G363" t="n">
-        <v>1405192</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -29270,25 +29270,25 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>1854</v>
+        <v>1811</v>
       </c>
       <c r="D364" t="n">
-        <v>1856.6</v>
+        <v>1850</v>
       </c>
       <c r="E364" t="n">
-        <v>1834.5</v>
+        <v>1806.1</v>
       </c>
       <c r="F364" t="n">
-        <v>1835</v>
+        <v>1850</v>
       </c>
       <c r="G364" t="n">
-        <v>2090998</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -29297,25 +29297,25 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1843</v>
+        <v>1854</v>
       </c>
       <c r="D365" t="n">
-        <v>1854.9</v>
+        <v>1856.6</v>
       </c>
       <c r="E365" t="n">
-        <v>1830</v>
+        <v>1834.5</v>
       </c>
       <c r="F365" t="n">
-        <v>1830</v>
+        <v>1835</v>
       </c>
       <c r="G365" t="n">
-        <v>2037418</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -29324,25 +29324,25 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1838</v>
+        <v>1843</v>
       </c>
       <c r="D366" t="n">
-        <v>1856</v>
+        <v>1854.9</v>
       </c>
       <c r="E366" t="n">
-        <v>1833.2</v>
+        <v>1830</v>
       </c>
       <c r="F366" t="n">
-        <v>1844.3</v>
+        <v>1830</v>
       </c>
       <c r="G366" t="n">
-        <v>1553067</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -29351,25 +29351,25 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1845</v>
+        <v>1838</v>
       </c>
       <c r="D367" t="n">
-        <v>1870.8</v>
+        <v>1856</v>
       </c>
       <c r="E367" t="n">
-        <v>1832.8</v>
+        <v>1833.2</v>
       </c>
       <c r="F367" t="n">
-        <v>1854</v>
+        <v>1844.3</v>
       </c>
       <c r="G367" t="n">
-        <v>1386592</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -29378,25 +29378,25 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>1851</v>
+        <v>1845</v>
       </c>
       <c r="D368" t="n">
-        <v>1859</v>
+        <v>1870.8</v>
       </c>
       <c r="E368" t="n">
-        <v>1833.1</v>
+        <v>1832.8</v>
       </c>
       <c r="F368" t="n">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="G368" t="n">
-        <v>1514239</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -29405,25 +29405,25 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1856.3</v>
+        <v>1851</v>
       </c>
       <c r="D369" t="n">
-        <v>1862.3</v>
+        <v>1859</v>
       </c>
       <c r="E369" t="n">
-        <v>1835</v>
+        <v>1833.1</v>
       </c>
       <c r="F369" t="n">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="G369" t="n">
-        <v>1088545</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -29432,25 +29432,25 @@
         </is>
       </c>
       <c r="C370" t="n">
+        <v>1856.3</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1862.3</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1835</v>
+      </c>
+      <c r="F370" t="n">
         <v>1850</v>
       </c>
-      <c r="D370" t="n">
-        <v>1851.7</v>
-      </c>
-      <c r="E370" t="n">
-        <v>1820.6</v>
-      </c>
-      <c r="F370" t="n">
-        <v>1851.7</v>
-      </c>
       <c r="G370" t="n">
-        <v>1345856</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -29459,25 +29459,25 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>1849.9</v>
+        <v>1850</v>
       </c>
       <c r="D371" t="n">
-        <v>1853.2</v>
+        <v>1851.7</v>
       </c>
       <c r="E371" t="n">
-        <v>1777.7</v>
+        <v>1820.6</v>
       </c>
       <c r="F371" t="n">
-        <v>1787.3</v>
+        <v>1851.7</v>
       </c>
       <c r="G371" t="n">
-        <v>1581352</v>
+        <v>1345856</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -29486,25 +29486,25 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1770</v>
+        <v>1849.9</v>
       </c>
       <c r="D372" t="n">
-        <v>1824</v>
+        <v>1853.2</v>
       </c>
       <c r="E372" t="n">
-        <v>1769.4</v>
+        <v>1777.7</v>
       </c>
       <c r="F372" t="n">
-        <v>1809.7</v>
+        <v>1787.3</v>
       </c>
       <c r="G372" t="n">
-        <v>1631767</v>
+        <v>1581352</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -29513,25 +29513,25 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>1810</v>
+        <v>1770</v>
       </c>
       <c r="D373" t="n">
-        <v>1824.6</v>
+        <v>1824</v>
       </c>
       <c r="E373" t="n">
-        <v>1802.1</v>
+        <v>1769.4</v>
       </c>
       <c r="F373" t="n">
-        <v>1814</v>
+        <v>1809.7</v>
       </c>
       <c r="G373" t="n">
-        <v>1291914</v>
+        <v>1631767</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -29540,25 +29540,25 @@
         </is>
       </c>
       <c r="C374" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1824.6</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1802.1</v>
+      </c>
+      <c r="F374" t="n">
         <v>1814</v>
       </c>
-      <c r="D374" t="n">
-        <v>1818</v>
-      </c>
-      <c r="E374" t="n">
-        <v>1789.9</v>
-      </c>
-      <c r="F374" t="n">
-        <v>1801.8</v>
-      </c>
       <c r="G374" t="n">
-        <v>1426377</v>
+        <v>1291914</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -29567,25 +29567,25 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="D375" t="n">
-        <v>1832</v>
+        <v>1818</v>
       </c>
       <c r="E375" t="n">
-        <v>1813.8</v>
+        <v>1789.9</v>
       </c>
       <c r="F375" t="n">
-        <v>1825</v>
+        <v>1801.8</v>
       </c>
       <c r="G375" t="n">
-        <v>1315065</v>
+        <v>1426377</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -29594,25 +29594,25 @@
         </is>
       </c>
       <c r="C376" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1813.8</v>
+      </c>
+      <c r="F376" t="n">
         <v>1825</v>
       </c>
-      <c r="D376" t="n">
-        <v>1836.4</v>
-      </c>
-      <c r="E376" t="n">
-        <v>1790.3</v>
-      </c>
-      <c r="F376" t="n">
-        <v>1802</v>
-      </c>
       <c r="G376" t="n">
-        <v>1401995</v>
+        <v>1315065</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -29621,25 +29621,25 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="D377" t="n">
-        <v>1810.8</v>
+        <v>1836.4</v>
       </c>
       <c r="E377" t="n">
-        <v>1790</v>
+        <v>1790.3</v>
       </c>
       <c r="F377" t="n">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="G377" t="n">
-        <v>2894242</v>
+        <v>1401995</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -29648,25 +29648,25 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="D378" t="n">
-        <v>1869.4</v>
+        <v>1810.8</v>
       </c>
       <c r="E378" t="n">
-        <v>1796.5</v>
+        <v>1790</v>
       </c>
       <c r="F378" t="n">
-        <v>1866.2</v>
+        <v>1801</v>
       </c>
       <c r="G378" t="n">
-        <v>3550945</v>
+        <v>2894242</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -29675,25 +29675,25 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1871.1</v>
+        <v>1808</v>
       </c>
       <c r="D379" t="n">
-        <v>1898.3</v>
+        <v>1869.4</v>
       </c>
       <c r="E379" t="n">
-        <v>1857.4</v>
+        <v>1796.5</v>
       </c>
       <c r="F379" t="n">
-        <v>1887</v>
+        <v>1866.2</v>
       </c>
       <c r="G379" t="n">
-        <v>3334188</v>
+        <v>3550945</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -29702,25 +29702,25 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1891.3</v>
+        <v>1871.1</v>
       </c>
       <c r="D380" t="n">
-        <v>1930</v>
+        <v>1898.3</v>
       </c>
       <c r="E380" t="n">
-        <v>1878.4</v>
+        <v>1857.4</v>
       </c>
       <c r="F380" t="n">
-        <v>1929.4</v>
+        <v>1887</v>
       </c>
       <c r="G380" t="n">
-        <v>4249869</v>
+        <v>3334188</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -29729,25 +29729,25 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1929.7</v>
+        <v>1891.3</v>
       </c>
       <c r="D381" t="n">
-        <v>1938.5</v>
+        <v>1930</v>
       </c>
       <c r="E381" t="n">
-        <v>1910.1</v>
+        <v>1878.4</v>
       </c>
       <c r="F381" t="n">
-        <v>1938.5</v>
+        <v>1929.4</v>
       </c>
       <c r="G381" t="n">
-        <v>2231476</v>
+        <v>4249869</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -29756,25 +29756,25 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1945</v>
+        <v>1929.7</v>
       </c>
       <c r="D382" t="n">
-        <v>1949</v>
+        <v>1938.5</v>
       </c>
       <c r="E382" t="n">
-        <v>1847.8</v>
+        <v>1910.1</v>
       </c>
       <c r="F382" t="n">
-        <v>1915</v>
+        <v>1938.5</v>
       </c>
       <c r="G382" t="n">
-        <v>30995343</v>
+        <v>2231476</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -29783,25 +29783,25 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1888.9</v>
+        <v>1945</v>
       </c>
       <c r="D383" t="n">
-        <v>1895</v>
+        <v>1949</v>
       </c>
       <c r="E383" t="n">
-        <v>1837.4</v>
+        <v>1847.8</v>
       </c>
       <c r="F383" t="n">
-        <v>1861.6</v>
+        <v>1915</v>
       </c>
       <c r="G383" t="n">
-        <v>3530385</v>
+        <v>30995343</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -29810,25 +29810,25 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1853.2</v>
+        <v>1888.9</v>
       </c>
       <c r="D384" t="n">
-        <v>1864.4</v>
+        <v>1895</v>
       </c>
       <c r="E384" t="n">
-        <v>1811.7</v>
+        <v>1837.4</v>
       </c>
       <c r="F384" t="n">
-        <v>1864</v>
+        <v>1861.6</v>
       </c>
       <c r="G384" t="n">
-        <v>2265630</v>
+        <v>3530385</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -29837,25 +29837,25 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1864.9</v>
+        <v>1853.2</v>
       </c>
       <c r="D385" t="n">
-        <v>1876.6</v>
+        <v>1864.4</v>
       </c>
       <c r="E385" t="n">
-        <v>1852.6</v>
+        <v>1811.7</v>
       </c>
       <c r="F385" t="n">
-        <v>1868.5</v>
+        <v>1864</v>
       </c>
       <c r="G385" t="n">
-        <v>1506361</v>
+        <v>2265630</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -29864,25 +29864,25 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1855</v>
+        <v>1864.9</v>
       </c>
       <c r="D386" t="n">
-        <v>1871.8</v>
+        <v>1876.6</v>
       </c>
       <c r="E386" t="n">
-        <v>1835.2</v>
+        <v>1852.6</v>
       </c>
       <c r="F386" t="n">
-        <v>1840</v>
+        <v>1868.5</v>
       </c>
       <c r="G386" t="n">
-        <v>1075943</v>
+        <v>1506361</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -29891,25 +29891,25 @@
         </is>
       </c>
       <c r="C387" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D387" t="n">
+        <v>1871.8</v>
+      </c>
+      <c r="E387" t="n">
+        <v>1835.2</v>
+      </c>
+      <c r="F387" t="n">
         <v>1840</v>
       </c>
-      <c r="D387" t="n">
-        <v>1876.7</v>
-      </c>
-      <c r="E387" t="n">
-        <v>1832.7</v>
-      </c>
-      <c r="F387" t="n">
-        <v>1876.7</v>
-      </c>
       <c r="G387" t="n">
-        <v>1148664</v>
+        <v>1075943</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -29918,25 +29918,25 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1870.8</v>
+        <v>1840</v>
       </c>
       <c r="D388" t="n">
-        <v>1952</v>
+        <v>1876.7</v>
       </c>
       <c r="E388" t="n">
-        <v>1862.7</v>
+        <v>1832.7</v>
       </c>
       <c r="F388" t="n">
-        <v>1946.9</v>
+        <v>1876.7</v>
       </c>
       <c r="G388" t="n">
-        <v>2115447</v>
+        <v>1148664</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -29945,25 +29945,25 @@
         </is>
       </c>
       <c r="C389" t="n">
+        <v>1870.8</v>
+      </c>
+      <c r="D389" t="n">
+        <v>1952</v>
+      </c>
+      <c r="E389" t="n">
+        <v>1862.7</v>
+      </c>
+      <c r="F389" t="n">
         <v>1946.9</v>
       </c>
-      <c r="D389" t="n">
-        <v>1955</v>
-      </c>
-      <c r="E389" t="n">
-        <v>1917.9</v>
-      </c>
-      <c r="F389" t="n">
-        <v>1937</v>
-      </c>
       <c r="G389" t="n">
-        <v>1822218</v>
+        <v>2115447</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -29972,25 +29972,25 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1932.6</v>
+        <v>1946.9</v>
       </c>
       <c r="D390" t="n">
-        <v>1950.5</v>
+        <v>1955</v>
       </c>
       <c r="E390" t="n">
-        <v>1920.9</v>
+        <v>1917.9</v>
       </c>
       <c r="F390" t="n">
-        <v>1945</v>
+        <v>1937</v>
       </c>
       <c r="G390" t="n">
-        <v>1067622</v>
+        <v>1822218</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -29999,25 +29999,25 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1943</v>
+        <v>1932.6</v>
       </c>
       <c r="D391" t="n">
-        <v>1981.8</v>
+        <v>1950.5</v>
       </c>
       <c r="E391" t="n">
-        <v>1918.1</v>
+        <v>1920.9</v>
       </c>
       <c r="F391" t="n">
-        <v>1969</v>
+        <v>1945</v>
       </c>
       <c r="G391" t="n">
-        <v>2277375</v>
+        <v>1067622</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -30026,25 +30026,25 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1969</v>
+        <v>1943</v>
       </c>
       <c r="D392" t="n">
-        <v>1969</v>
+        <v>1981.8</v>
       </c>
       <c r="E392" t="n">
-        <v>1969</v>
+        <v>1918.1</v>
       </c>
       <c r="F392" t="n">
         <v>1969</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>2277375</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -30053,25 +30053,25 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1975</v>
+        <v>1969</v>
       </c>
       <c r="D393" t="n">
-        <v>1981</v>
+        <v>1969</v>
       </c>
       <c r="E393" t="n">
-        <v>1915.6</v>
+        <v>1969</v>
       </c>
       <c r="F393" t="n">
-        <v>1926.9</v>
+        <v>1969</v>
       </c>
       <c r="G393" t="n">
-        <v>1538262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -30080,25 +30080,25 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1924.6</v>
+        <v>1975</v>
       </c>
       <c r="D394" t="n">
-        <v>1940.4</v>
+        <v>1981</v>
       </c>
       <c r="E394" t="n">
-        <v>1863.5</v>
+        <v>1915.6</v>
       </c>
       <c r="F394" t="n">
-        <v>1905.5</v>
+        <v>1926.9</v>
       </c>
       <c r="G394" t="n">
-        <v>2871410</v>
+        <v>1538262</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -30107,25 +30107,25 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1898</v>
+        <v>1924.6</v>
       </c>
       <c r="D395" t="n">
-        <v>1964.5</v>
+        <v>1940.4</v>
       </c>
       <c r="E395" t="n">
-        <v>1894.8</v>
+        <v>1863.5</v>
       </c>
       <c r="F395" t="n">
-        <v>1948.1</v>
+        <v>1905.5</v>
       </c>
       <c r="G395" t="n">
-        <v>1645108</v>
+        <v>2871410</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -30134,25 +30134,25 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>1962</v>
+        <v>1898</v>
       </c>
       <c r="D396" t="n">
-        <v>1982</v>
+        <v>1964.5</v>
       </c>
       <c r="E396" t="n">
-        <v>1954</v>
+        <v>1894.8</v>
       </c>
       <c r="F396" t="n">
-        <v>1954</v>
+        <v>1948.1</v>
       </c>
       <c r="G396" t="n">
-        <v>2655873</v>
+        <v>1645108</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -30161,25 +30161,25 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1966.6</v>
+        <v>1962</v>
       </c>
       <c r="D397" t="n">
-        <v>2023.5</v>
+        <v>1982</v>
       </c>
       <c r="E397" t="n">
-        <v>1963.8</v>
+        <v>1954</v>
       </c>
       <c r="F397" t="n">
-        <v>2017.5</v>
+        <v>1954</v>
       </c>
       <c r="G397" t="n">
-        <v>2170267</v>
+        <v>2655873</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -30188,25 +30188,25 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2018</v>
+        <v>1966.6</v>
       </c>
       <c r="D398" t="n">
-        <v>2032.8</v>
+        <v>2023.5</v>
       </c>
       <c r="E398" t="n">
-        <v>2002.2</v>
+        <v>1963.8</v>
       </c>
       <c r="F398" t="n">
-        <v>2006.5</v>
+        <v>2017.5</v>
       </c>
       <c r="G398" t="n">
-        <v>1487044</v>
+        <v>2170267</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -30215,25 +30215,25 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2009.5</v>
+        <v>2018</v>
       </c>
       <c r="D399" t="n">
-        <v>2037.2</v>
+        <v>2032.8</v>
       </c>
       <c r="E399" t="n">
-        <v>1999.7</v>
+        <v>2002.2</v>
       </c>
       <c r="F399" t="n">
-        <v>2034</v>
+        <v>2006.5</v>
       </c>
       <c r="G399" t="n">
-        <v>1363988</v>
+        <v>1487044</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -30242,25 +30242,25 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2021.1</v>
+        <v>2009.5</v>
       </c>
       <c r="D400" t="n">
-        <v>2055.3</v>
+        <v>2037.2</v>
       </c>
       <c r="E400" t="n">
-        <v>2020</v>
+        <v>1999.7</v>
       </c>
       <c r="F400" t="n">
-        <v>2026.2</v>
+        <v>2034</v>
       </c>
       <c r="G400" t="n">
-        <v>1388039</v>
+        <v>1363988</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -30269,25 +30269,25 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2026</v>
+        <v>2021.1</v>
       </c>
       <c r="D401" t="n">
-        <v>2040</v>
+        <v>2055.3</v>
       </c>
       <c r="E401" t="n">
-        <v>1979.2</v>
+        <v>2020</v>
       </c>
       <c r="F401" t="n">
-        <v>2007</v>
+        <v>2026.2</v>
       </c>
       <c r="G401" t="n">
-        <v>1442142</v>
+        <v>1388039</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -30296,25 +30296,25 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D402" t="n">
-        <v>2012.3</v>
+        <v>2040</v>
       </c>
       <c r="E402" t="n">
-        <v>1984.8</v>
+        <v>1979.2</v>
       </c>
       <c r="F402" t="n">
-        <v>2010.7</v>
+        <v>2007</v>
       </c>
       <c r="G402" t="n">
-        <v>950451</v>
+        <v>1442142</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -30323,25 +30323,25 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2020.7</v>
+        <v>2000</v>
       </c>
       <c r="D403" t="n">
-        <v>2024.9</v>
+        <v>2012.3</v>
       </c>
       <c r="E403" t="n">
-        <v>1979</v>
+        <v>1984.8</v>
       </c>
       <c r="F403" t="n">
-        <v>1979</v>
+        <v>2010.7</v>
       </c>
       <c r="G403" t="n">
-        <v>2431575</v>
+        <v>950451</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -30350,25 +30350,25 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>1993</v>
+        <v>2020.7</v>
       </c>
       <c r="D404" t="n">
-        <v>2001.6</v>
+        <v>2024.9</v>
       </c>
       <c r="E404" t="n">
-        <v>1955.1</v>
+        <v>1979</v>
       </c>
       <c r="F404" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="G404" t="n">
-        <v>1397926</v>
+        <v>2431575</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -30377,25 +30377,25 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>1973.6</v>
+        <v>1993</v>
       </c>
       <c r="D405" t="n">
-        <v>2006.9</v>
+        <v>2001.6</v>
       </c>
       <c r="E405" t="n">
-        <v>1952.1</v>
+        <v>1955.1</v>
       </c>
       <c r="F405" t="n">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="G405" t="n">
-        <v>1459687</v>
+        <v>1397926</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -30404,25 +30404,25 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1984</v>
+        <v>1973.6</v>
       </c>
       <c r="D406" t="n">
-        <v>1984</v>
+        <v>2006.9</v>
       </c>
       <c r="E406" t="n">
-        <v>1984</v>
+        <v>1952.1</v>
       </c>
       <c r="F406" t="n">
         <v>1984</v>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
+        <v>1459687</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -30431,52 +30431,52 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1994</v>
+        <v>1984</v>
       </c>
       <c r="D407" t="n">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="E407" t="n">
-        <v>1955.1</v>
+        <v>1984</v>
       </c>
       <c r="F407" t="n">
-        <v>1971.4</v>
+        <v>1984</v>
       </c>
       <c r="G407" t="n">
-        <v>1374138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3350</v>
+        <v>1994</v>
       </c>
       <c r="D408" t="n">
-        <v>3366.4</v>
+        <v>2002</v>
       </c>
       <c r="E408" t="n">
-        <v>3279.9</v>
+        <v>1955.1</v>
       </c>
       <c r="F408" t="n">
-        <v>3342</v>
+        <v>1971.4</v>
       </c>
       <c r="G408" t="n">
-        <v>1433417</v>
+        <v>1374138</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -30485,25 +30485,25 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>3362</v>
+        <v>3350</v>
       </c>
       <c r="D409" t="n">
-        <v>3398</v>
+        <v>3366.4</v>
       </c>
       <c r="E409" t="n">
-        <v>3323.5</v>
+        <v>3279.9</v>
       </c>
       <c r="F409" t="n">
-        <v>3350</v>
+        <v>3342</v>
       </c>
       <c r="G409" t="n">
-        <v>2174879</v>
+        <v>1433417</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -30512,25 +30512,25 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>3311.9</v>
+        <v>3362</v>
       </c>
       <c r="D410" t="n">
-        <v>3335.5</v>
+        <v>3398</v>
       </c>
       <c r="E410" t="n">
-        <v>3285</v>
+        <v>3323.5</v>
       </c>
       <c r="F410" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="G410" t="n">
-        <v>1308638</v>
+        <v>2174879</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -30539,25 +30539,25 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3326</v>
+        <v>3311.9</v>
       </c>
       <c r="D411" t="n">
-        <v>3389</v>
+        <v>3335.5</v>
       </c>
       <c r="E411" t="n">
-        <v>3247.2</v>
+        <v>3285</v>
       </c>
       <c r="F411" t="n">
-        <v>3276</v>
+        <v>3300</v>
       </c>
       <c r="G411" t="n">
-        <v>1686562</v>
+        <v>1308638</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -30566,25 +30566,25 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>3276</v>
+        <v>3326</v>
       </c>
       <c r="D412" t="n">
-        <v>3276</v>
+        <v>3389</v>
       </c>
       <c r="E412" t="n">
-        <v>3276</v>
+        <v>3247.2</v>
       </c>
       <c r="F412" t="n">
         <v>3276</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>1686562</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -30593,25 +30593,25 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3265</v>
+        <v>3276</v>
       </c>
       <c r="D413" t="n">
-        <v>3267.6</v>
+        <v>3276</v>
       </c>
       <c r="E413" t="n">
-        <v>3156.4</v>
+        <v>3276</v>
       </c>
       <c r="F413" t="n">
-        <v>3173.5</v>
+        <v>3276</v>
       </c>
       <c r="G413" t="n">
-        <v>1746940</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -30620,25 +30620,25 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>3170.2</v>
+        <v>3265</v>
       </c>
       <c r="D414" t="n">
-        <v>3224.5</v>
+        <v>3267.6</v>
       </c>
       <c r="E414" t="n">
-        <v>3056.6</v>
+        <v>3156.4</v>
       </c>
       <c r="F414" t="n">
-        <v>3211.2</v>
+        <v>3173.5</v>
       </c>
       <c r="G414" t="n">
-        <v>1971522</v>
+        <v>1746940</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -30647,25 +30647,25 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3201.1</v>
+        <v>3170.2</v>
       </c>
       <c r="D415" t="n">
-        <v>3304</v>
+        <v>3224.5</v>
       </c>
       <c r="E415" t="n">
-        <v>3180.1</v>
+        <v>3056.6</v>
       </c>
       <c r="F415" t="n">
-        <v>3265.2</v>
+        <v>3211.2</v>
       </c>
       <c r="G415" t="n">
-        <v>1530935</v>
+        <v>1971522</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -30674,25 +30674,25 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>3257.5</v>
+        <v>3201.1</v>
       </c>
       <c r="D416" t="n">
-        <v>3314.9</v>
+        <v>3304</v>
       </c>
       <c r="E416" t="n">
-        <v>3230.1</v>
+        <v>3180.1</v>
       </c>
       <c r="F416" t="n">
-        <v>3260</v>
+        <v>3265.2</v>
       </c>
       <c r="G416" t="n">
-        <v>2197423</v>
+        <v>1530935</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -30701,25 +30701,25 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3250</v>
+        <v>3257.5</v>
       </c>
       <c r="D417" t="n">
-        <v>3268</v>
+        <v>3314.9</v>
       </c>
       <c r="E417" t="n">
-        <v>3155.5</v>
+        <v>3230.1</v>
       </c>
       <c r="F417" t="n">
-        <v>3209</v>
+        <v>3260</v>
       </c>
       <c r="G417" t="n">
-        <v>1267161</v>
+        <v>2197423</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -30728,25 +30728,25 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3220</v>
+        <v>3250</v>
       </c>
       <c r="D418" t="n">
-        <v>3289.8</v>
+        <v>3268</v>
       </c>
       <c r="E418" t="n">
-        <v>3212.8</v>
+        <v>3155.5</v>
       </c>
       <c r="F418" t="n">
-        <v>3262.6</v>
+        <v>3209</v>
       </c>
       <c r="G418" t="n">
-        <v>1069125</v>
+        <v>1267161</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -30755,25 +30755,25 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3269</v>
+        <v>3220</v>
       </c>
       <c r="D419" t="n">
-        <v>3374</v>
+        <v>3289.8</v>
       </c>
       <c r="E419" t="n">
-        <v>3237.5</v>
+        <v>3212.8</v>
       </c>
       <c r="F419" t="n">
-        <v>3374</v>
+        <v>3262.6</v>
       </c>
       <c r="G419" t="n">
-        <v>2249890</v>
+        <v>1069125</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -30782,25 +30782,25 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3365</v>
+        <v>3269</v>
       </c>
       <c r="D420" t="n">
-        <v>3477</v>
+        <v>3374</v>
       </c>
       <c r="E420" t="n">
-        <v>3351.1</v>
+        <v>3237.5</v>
       </c>
       <c r="F420" t="n">
-        <v>3427.7</v>
+        <v>3374</v>
       </c>
       <c r="G420" t="n">
-        <v>4133428</v>
+        <v>2249890</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -30809,25 +30809,25 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>3463.6</v>
+        <v>3365</v>
       </c>
       <c r="D421" t="n">
-        <v>3481.4</v>
+        <v>3477</v>
       </c>
       <c r="E421" t="n">
-        <v>3310</v>
+        <v>3351.1</v>
       </c>
       <c r="F421" t="n">
-        <v>3324.9</v>
+        <v>3427.7</v>
       </c>
       <c r="G421" t="n">
-        <v>2386852</v>
+        <v>4133428</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -30836,25 +30836,25 @@
         </is>
       </c>
       <c r="C422" t="n">
+        <v>3463.6</v>
+      </c>
+      <c r="D422" t="n">
+        <v>3481.4</v>
+      </c>
+      <c r="E422" t="n">
         <v>3310</v>
       </c>
-      <c r="D422" t="n">
-        <v>3321</v>
-      </c>
-      <c r="E422" t="n">
-        <v>3251.7</v>
-      </c>
       <c r="F422" t="n">
-        <v>3263.5</v>
+        <v>3324.9</v>
       </c>
       <c r="G422" t="n">
-        <v>1090601</v>
+        <v>2386852</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -30863,25 +30863,25 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>3248</v>
+        <v>3310</v>
       </c>
       <c r="D423" t="n">
-        <v>3344</v>
+        <v>3321</v>
       </c>
       <c r="E423" t="n">
-        <v>3232</v>
+        <v>3251.7</v>
       </c>
       <c r="F423" t="n">
-        <v>3232</v>
+        <v>3263.5</v>
       </c>
       <c r="G423" t="n">
-        <v>2094968</v>
+        <v>1090601</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -30890,25 +30890,25 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>3280.1</v>
+        <v>3248</v>
       </c>
       <c r="D424" t="n">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="E424" t="n">
-        <v>3255</v>
+        <v>3232</v>
       </c>
       <c r="F424" t="n">
-        <v>3300.4</v>
+        <v>3232</v>
       </c>
       <c r="G424" t="n">
-        <v>2066935</v>
+        <v>2094968</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -30917,25 +30917,25 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>3300</v>
+        <v>3280.1</v>
       </c>
       <c r="D425" t="n">
-        <v>3331.3</v>
+        <v>3345</v>
       </c>
       <c r="E425" t="n">
-        <v>3193.6</v>
+        <v>3255</v>
       </c>
       <c r="F425" t="n">
-        <v>3204</v>
+        <v>3300.4</v>
       </c>
       <c r="G425" t="n">
-        <v>2002629</v>
+        <v>2066935</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -30944,25 +30944,25 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>3204</v>
+        <v>3300</v>
       </c>
       <c r="D426" t="n">
-        <v>3204</v>
+        <v>3331.3</v>
       </c>
       <c r="E426" t="n">
-        <v>3204</v>
+        <v>3193.6</v>
       </c>
       <c r="F426" t="n">
         <v>3204</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>2002629</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -30971,52 +30971,52 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>3220</v>
+        <v>3204</v>
       </c>
       <c r="D427" t="n">
-        <v>3258.7</v>
+        <v>3204</v>
       </c>
       <c r="E427" t="n">
-        <v>3150</v>
+        <v>3204</v>
       </c>
       <c r="F427" t="n">
-        <v>3181.7</v>
+        <v>3204</v>
       </c>
       <c r="G427" t="n">
-        <v>1386833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>344</v>
+        <v>3220</v>
       </c>
       <c r="D428" t="n">
-        <v>346.3</v>
+        <v>3258.7</v>
       </c>
       <c r="E428" t="n">
-        <v>341.25</v>
+        <v>3150</v>
       </c>
       <c r="F428" t="n">
-        <v>342.9</v>
+        <v>3181.7</v>
       </c>
       <c r="G428" t="n">
-        <v>4465145</v>
+        <v>1386833</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -31025,25 +31025,25 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>344.2</v>
+        <v>344</v>
       </c>
       <c r="D429" t="n">
-        <v>347.75</v>
+        <v>346.3</v>
       </c>
       <c r="E429" t="n">
-        <v>339.95</v>
+        <v>341.25</v>
       </c>
       <c r="F429" t="n">
-        <v>342.4</v>
+        <v>342.9</v>
       </c>
       <c r="G429" t="n">
-        <v>3803051</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -31052,25 +31052,25 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>346</v>
+        <v>344.2</v>
       </c>
       <c r="D430" t="n">
-        <v>351</v>
+        <v>347.75</v>
       </c>
       <c r="E430" t="n">
-        <v>343.65</v>
+        <v>339.95</v>
       </c>
       <c r="F430" t="n">
-        <v>346</v>
+        <v>342.4</v>
       </c>
       <c r="G430" t="n">
-        <v>5175178</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -31079,25 +31079,25 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>341.8</v>
+        <v>346</v>
       </c>
       <c r="D431" t="n">
-        <v>344.9</v>
+        <v>351</v>
       </c>
       <c r="E431" t="n">
-        <v>339.65</v>
+        <v>343.65</v>
       </c>
       <c r="F431" t="n">
-        <v>343.9</v>
+        <v>346</v>
       </c>
       <c r="G431" t="n">
-        <v>2253982</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -31106,25 +31106,25 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>345.1</v>
+        <v>341.8</v>
       </c>
       <c r="D432" t="n">
-        <v>346.05</v>
+        <v>344.9</v>
       </c>
       <c r="E432" t="n">
-        <v>338.35</v>
+        <v>339.65</v>
       </c>
       <c r="F432" t="n">
-        <v>339.35</v>
+        <v>343.9</v>
       </c>
       <c r="G432" t="n">
-        <v>3868006</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -31133,25 +31133,25 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>339.4</v>
+        <v>345.1</v>
       </c>
       <c r="D433" t="n">
-        <v>340.2</v>
+        <v>346.05</v>
       </c>
       <c r="E433" t="n">
-        <v>333</v>
+        <v>338.35</v>
       </c>
       <c r="F433" t="n">
-        <v>334.55</v>
+        <v>339.35</v>
       </c>
       <c r="G433" t="n">
-        <v>3721274</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -31160,25 +31160,25 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>335</v>
+        <v>339.4</v>
       </c>
       <c r="D434" t="n">
-        <v>346.1</v>
+        <v>340.2</v>
       </c>
       <c r="E434" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F434" t="n">
-        <v>344.7</v>
+        <v>334.55</v>
       </c>
       <c r="G434" t="n">
-        <v>5431501</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -31187,25 +31187,25 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>345.5</v>
+        <v>335</v>
       </c>
       <c r="D435" t="n">
-        <v>349.65</v>
+        <v>346.1</v>
       </c>
       <c r="E435" t="n">
-        <v>342.6</v>
+        <v>332</v>
       </c>
       <c r="F435" t="n">
-        <v>347.65</v>
+        <v>344.7</v>
       </c>
       <c r="G435" t="n">
-        <v>6318472</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -31214,25 +31214,25 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>352</v>
+        <v>345.5</v>
       </c>
       <c r="D436" t="n">
-        <v>355.75</v>
+        <v>349.65</v>
       </c>
       <c r="E436" t="n">
+        <v>342.6</v>
+      </c>
+      <c r="F436" t="n">
         <v>347.65</v>
       </c>
-      <c r="F436" t="n">
-        <v>350.05</v>
-      </c>
       <c r="G436" t="n">
-        <v>7186013</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -31241,25 +31241,25 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>357.95</v>
+        <v>352</v>
       </c>
       <c r="D437" t="n">
-        <v>369</v>
+        <v>355.75</v>
       </c>
       <c r="E437" t="n">
-        <v>353.5</v>
+        <v>347.65</v>
       </c>
       <c r="F437" t="n">
-        <v>369</v>
+        <v>350.05</v>
       </c>
       <c r="G437" t="n">
-        <v>12541474</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -31268,25 +31268,25 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>373</v>
+        <v>357.95</v>
       </c>
       <c r="D438" t="n">
-        <v>382.45</v>
+        <v>369</v>
       </c>
       <c r="E438" t="n">
-        <v>367.15</v>
+        <v>353.5</v>
       </c>
       <c r="F438" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="G438" t="n">
-        <v>15775994</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -31295,25 +31295,25 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D439" t="n">
-        <v>383.9</v>
+        <v>382.45</v>
       </c>
       <c r="E439" t="n">
-        <v>375.15</v>
+        <v>367.15</v>
       </c>
       <c r="F439" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G439" t="n">
-        <v>8940938</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -31322,25 +31322,25 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D440" t="n">
-        <v>385.05</v>
+        <v>383.9</v>
       </c>
       <c r="E440" t="n">
-        <v>376.5</v>
+        <v>375.15</v>
       </c>
       <c r="F440" t="n">
         <v>381</v>
       </c>
       <c r="G440" t="n">
-        <v>6636333</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -31349,25 +31349,25 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>382.5</v>
+        <v>385</v>
       </c>
       <c r="D441" t="n">
-        <v>382.85</v>
+        <v>385.05</v>
       </c>
       <c r="E441" t="n">
-        <v>377.15</v>
+        <v>376.5</v>
       </c>
       <c r="F441" t="n">
         <v>381</v>
       </c>
       <c r="G441" t="n">
-        <v>4423953</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -31376,25 +31376,25 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>381.7</v>
+        <v>382.5</v>
       </c>
       <c r="D442" t="n">
-        <v>387.7</v>
+        <v>382.85</v>
       </c>
       <c r="E442" t="n">
-        <v>381.1</v>
+        <v>377.15</v>
       </c>
       <c r="F442" t="n">
-        <v>382.7</v>
+        <v>381</v>
       </c>
       <c r="G442" t="n">
-        <v>5292453</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -31403,25 +31403,25 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>387.15</v>
+        <v>381.7</v>
       </c>
       <c r="D443" t="n">
-        <v>393.7</v>
+        <v>387.7</v>
       </c>
       <c r="E443" t="n">
-        <v>384.5</v>
+        <v>381.1</v>
       </c>
       <c r="F443" t="n">
-        <v>388</v>
+        <v>382.7</v>
       </c>
       <c r="G443" t="n">
-        <v>8155315</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -31430,25 +31430,25 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>397.49</v>
+        <v>387.15</v>
       </c>
       <c r="D444" t="n">
-        <v>421.13</v>
+        <v>393.7</v>
       </c>
       <c r="E444" t="n">
-        <v>397.49</v>
+        <v>384.5</v>
       </c>
       <c r="F444" t="n">
-        <v>418.94</v>
+        <v>388</v>
       </c>
       <c r="G444" t="n">
-        <v>34388331</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -31457,25 +31457,25 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>409.46</v>
+        <v>397.49</v>
       </c>
       <c r="D445" t="n">
-        <v>412.6</v>
+        <v>421.13</v>
       </c>
       <c r="E445" t="n">
-        <v>398.99</v>
+        <v>397.49</v>
       </c>
       <c r="F445" t="n">
-        <v>399.48</v>
+        <v>418.94</v>
       </c>
       <c r="G445" t="n">
-        <v>9738984</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -31484,25 +31484,25 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>377.64</v>
+        <v>409.46</v>
       </c>
       <c r="D446" t="n">
-        <v>383.97</v>
+        <v>412.6</v>
       </c>
       <c r="E446" t="n">
-        <v>374.05</v>
+        <v>398.99</v>
       </c>
       <c r="F446" t="n">
-        <v>375.05</v>
+        <v>399.48</v>
       </c>
       <c r="G446" t="n">
-        <v>14954594</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -31511,25 +31511,25 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>376.94</v>
+        <v>377.64</v>
       </c>
       <c r="D447" t="n">
-        <v>390.51</v>
+        <v>383.97</v>
       </c>
       <c r="E447" t="n">
-        <v>375.55</v>
+        <v>374.05</v>
       </c>
       <c r="F447" t="n">
-        <v>386.57</v>
+        <v>375.05</v>
       </c>
       <c r="G447" t="n">
-        <v>9724992</v>
+        <v>14954594</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -31538,25 +31538,25 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>385.82</v>
+        <v>376.94</v>
       </c>
       <c r="D448" t="n">
-        <v>389.86</v>
+        <v>390.51</v>
       </c>
       <c r="E448" t="n">
-        <v>384.82</v>
+        <v>375.55</v>
       </c>
       <c r="F448" t="n">
-        <v>387.02</v>
+        <v>386.57</v>
       </c>
       <c r="G448" t="n">
-        <v>2824411</v>
+        <v>9724992</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -31565,25 +31565,25 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>381.03</v>
+        <v>385.82</v>
       </c>
       <c r="D449" t="n">
-        <v>385.57</v>
+        <v>389.86</v>
       </c>
       <c r="E449" t="n">
-        <v>378.04</v>
+        <v>384.82</v>
       </c>
       <c r="F449" t="n">
-        <v>385.57</v>
+        <v>387.02</v>
       </c>
       <c r="G449" t="n">
-        <v>3939022</v>
+        <v>2824411</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -31592,25 +31592,25 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>391.01</v>
+        <v>381.03</v>
       </c>
       <c r="D450" t="n">
-        <v>394.75</v>
+        <v>385.57</v>
       </c>
       <c r="E450" t="n">
-        <v>384.12</v>
+        <v>378.04</v>
       </c>
       <c r="F450" t="n">
-        <v>384.62</v>
+        <v>385.57</v>
       </c>
       <c r="G450" t="n">
-        <v>5349753</v>
+        <v>3939022</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -31619,25 +31619,25 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>387.02</v>
+        <v>391.01</v>
       </c>
       <c r="D451" t="n">
-        <v>396.49</v>
+        <v>394.75</v>
       </c>
       <c r="E451" t="n">
-        <v>383.62</v>
+        <v>384.12</v>
       </c>
       <c r="F451" t="n">
-        <v>393.45</v>
+        <v>384.62</v>
       </c>
       <c r="G451" t="n">
-        <v>6393431</v>
+        <v>5349753</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -31646,25 +31646,25 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>398.45</v>
+        <v>387.02</v>
       </c>
       <c r="D452" t="n">
-        <v>405</v>
+        <v>396.49</v>
       </c>
       <c r="E452" t="n">
-        <v>397.5</v>
+        <v>383.62</v>
       </c>
       <c r="F452" t="n">
-        <v>403.3</v>
+        <v>393.45</v>
       </c>
       <c r="G452" t="n">
-        <v>7285035</v>
+        <v>6393431</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -31673,25 +31673,25 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>402</v>
+        <v>398.45</v>
       </c>
       <c r="D453" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E453" t="n">
-        <v>392.05</v>
+        <v>397.5</v>
       </c>
       <c r="F453" t="n">
-        <v>397.8</v>
+        <v>403.3</v>
       </c>
       <c r="G453" t="n">
-        <v>3855735</v>
+        <v>7285035</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -31700,25 +31700,25 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>397.7</v>
+        <v>402</v>
       </c>
       <c r="D454" t="n">
-        <v>400.45</v>
+        <v>402</v>
       </c>
       <c r="E454" t="n">
-        <v>393</v>
+        <v>392.05</v>
       </c>
       <c r="F454" t="n">
-        <v>399.3</v>
+        <v>397.8</v>
       </c>
       <c r="G454" t="n">
-        <v>3087665</v>
+        <v>3855735</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -31727,25 +31727,25 @@
         </is>
       </c>
       <c r="C455" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="D455" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="E455" t="n">
+        <v>393</v>
+      </c>
+      <c r="F455" t="n">
         <v>399.3</v>
       </c>
-      <c r="D455" t="n">
-        <v>403.35</v>
-      </c>
-      <c r="E455" t="n">
-        <v>388</v>
-      </c>
-      <c r="F455" t="n">
-        <v>389.3</v>
-      </c>
       <c r="G455" t="n">
-        <v>2903197</v>
+        <v>3087665</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -31754,25 +31754,25 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>392.65</v>
+        <v>399.3</v>
       </c>
       <c r="D456" t="n">
-        <v>394.95</v>
+        <v>403.35</v>
       </c>
       <c r="E456" t="n">
+        <v>388</v>
+      </c>
+      <c r="F456" t="n">
         <v>389.3</v>
       </c>
-      <c r="F456" t="n">
-        <v>394.95</v>
-      </c>
       <c r="G456" t="n">
-        <v>1868958</v>
+        <v>2903197</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -31781,25 +31781,25 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>390</v>
+        <v>392.65</v>
       </c>
       <c r="D457" t="n">
-        <v>392</v>
+        <v>394.95</v>
       </c>
       <c r="E457" t="n">
-        <v>377.15</v>
+        <v>389.3</v>
       </c>
       <c r="F457" t="n">
-        <v>381.5</v>
+        <v>394.95</v>
       </c>
       <c r="G457" t="n">
-        <v>11959002</v>
+        <v>1868958</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -31808,25 +31808,25 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D458" t="n">
-        <v>383.75</v>
+        <v>392</v>
       </c>
       <c r="E458" t="n">
-        <v>368.6</v>
+        <v>377.15</v>
       </c>
       <c r="F458" t="n">
-        <v>372</v>
+        <v>381.5</v>
       </c>
       <c r="G458" t="n">
-        <v>6155527</v>
+        <v>11959002</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -31835,25 +31835,25 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>371.65</v>
+        <v>383</v>
       </c>
       <c r="D459" t="n">
-        <v>373.5</v>
+        <v>383.75</v>
       </c>
       <c r="E459" t="n">
-        <v>367.5</v>
+        <v>368.6</v>
       </c>
       <c r="F459" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G459" t="n">
-        <v>4447742</v>
+        <v>6155527</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -31862,25 +31862,25 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>374</v>
+        <v>371.65</v>
       </c>
       <c r="D460" t="n">
-        <v>378.5</v>
+        <v>373.5</v>
       </c>
       <c r="E460" t="n">
-        <v>370.55</v>
+        <v>367.5</v>
       </c>
       <c r="F460" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G460" t="n">
-        <v>3760490</v>
+        <v>4447742</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -31889,25 +31889,25 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D461" t="n">
-        <v>378.95</v>
+        <v>378.5</v>
       </c>
       <c r="E461" t="n">
-        <v>372.75</v>
+        <v>370.55</v>
       </c>
       <c r="F461" t="n">
-        <v>374.1</v>
+        <v>374</v>
       </c>
       <c r="G461" t="n">
-        <v>5517970</v>
+        <v>3760490</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -31916,25 +31916,25 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>376.05</v>
+        <v>376</v>
       </c>
       <c r="D462" t="n">
-        <v>377.5</v>
+        <v>378.95</v>
       </c>
       <c r="E462" t="n">
-        <v>365.9</v>
+        <v>372.75</v>
       </c>
       <c r="F462" t="n">
-        <v>365.9</v>
+        <v>374.1</v>
       </c>
       <c r="G462" t="n">
-        <v>3280288</v>
+        <v>5517970</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -31943,25 +31943,25 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>370.7</v>
+        <v>376.05</v>
       </c>
       <c r="D463" t="n">
-        <v>378.3</v>
+        <v>377.5</v>
       </c>
       <c r="E463" t="n">
-        <v>367.8</v>
+        <v>365.9</v>
       </c>
       <c r="F463" t="n">
-        <v>371.05</v>
+        <v>365.9</v>
       </c>
       <c r="G463" t="n">
-        <v>5469151</v>
+        <v>3280288</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -31970,25 +31970,25 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>372</v>
+        <v>370.7</v>
       </c>
       <c r="D464" t="n">
-        <v>386</v>
+        <v>378.3</v>
       </c>
       <c r="E464" t="n">
-        <v>371.65</v>
+        <v>367.8</v>
       </c>
       <c r="F464" t="n">
-        <v>377.6</v>
+        <v>371.05</v>
       </c>
       <c r="G464" t="n">
-        <v>9139475</v>
+        <v>5469151</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -31997,25 +31997,25 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D465" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E465" t="n">
-        <v>371.05</v>
+        <v>371.65</v>
       </c>
       <c r="F465" t="n">
-        <v>373.35</v>
+        <v>377.6</v>
       </c>
       <c r="G465" t="n">
-        <v>3376100</v>
+        <v>9139475</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -32024,25 +32024,25 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="D466" t="n">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="E466" t="n">
-        <v>352.35</v>
+        <v>371.05</v>
       </c>
       <c r="F466" t="n">
-        <v>361</v>
+        <v>373.35</v>
       </c>
       <c r="G466" t="n">
-        <v>6560514</v>
+        <v>3376100</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -32051,25 +32051,25 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D467" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E467" t="n">
-        <v>361</v>
+        <v>352.35</v>
       </c>
       <c r="F467" t="n">
         <v>361</v>
       </c>
       <c r="G467" t="n">
-        <v>0</v>
+        <v>6560514</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -32078,25 +32078,25 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>359.6</v>
+        <v>361</v>
       </c>
       <c r="D468" t="n">
-        <v>360.35</v>
+        <v>361</v>
       </c>
       <c r="E468" t="n">
-        <v>350.25</v>
+        <v>361</v>
       </c>
       <c r="F468" t="n">
-        <v>350.55</v>
+        <v>361</v>
       </c>
       <c r="G468" t="n">
-        <v>3640356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -32105,25 +32105,25 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>352</v>
+        <v>359.6</v>
       </c>
       <c r="D469" t="n">
-        <v>357.75</v>
+        <v>360.35</v>
       </c>
       <c r="E469" t="n">
-        <v>350.1</v>
+        <v>350.25</v>
       </c>
       <c r="F469" t="n">
-        <v>356</v>
+        <v>350.55</v>
       </c>
       <c r="G469" t="n">
-        <v>3670150</v>
+        <v>3640356</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -32132,25 +32132,25 @@
         </is>
       </c>
       <c r="C470" t="n">
+        <v>352</v>
+      </c>
+      <c r="D470" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="E470" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="F470" t="n">
         <v>356</v>
       </c>
-      <c r="D470" t="n">
-        <v>360.75</v>
-      </c>
-      <c r="E470" t="n">
-        <v>354.2</v>
-      </c>
-      <c r="F470" t="n">
-        <v>355.7</v>
-      </c>
       <c r="G470" t="n">
-        <v>3033265</v>
+        <v>3670150</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -32159,25 +32159,25 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>359.8</v>
+        <v>356</v>
       </c>
       <c r="D471" t="n">
-        <v>363.2</v>
+        <v>360.75</v>
       </c>
       <c r="E471" t="n">
-        <v>350.5</v>
+        <v>354.2</v>
       </c>
       <c r="F471" t="n">
-        <v>350.5</v>
+        <v>355.7</v>
       </c>
       <c r="G471" t="n">
-        <v>5809441</v>
+        <v>3033265</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -32186,25 +32186,25 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>355.3</v>
+        <v>359.8</v>
       </c>
       <c r="D472" t="n">
-        <v>357.4</v>
+        <v>363.2</v>
       </c>
       <c r="E472" t="n">
-        <v>351.55</v>
+        <v>350.5</v>
       </c>
       <c r="F472" t="n">
-        <v>352.5</v>
+        <v>350.5</v>
       </c>
       <c r="G472" t="n">
-        <v>2961381</v>
+        <v>5809441</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -32213,25 +32213,25 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>352.95</v>
+        <v>355.3</v>
       </c>
       <c r="D473" t="n">
-        <v>353.2</v>
+        <v>357.4</v>
       </c>
       <c r="E473" t="n">
-        <v>348.1</v>
+        <v>351.55</v>
       </c>
       <c r="F473" t="n">
-        <v>352.2</v>
+        <v>352.5</v>
       </c>
       <c r="G473" t="n">
-        <v>2687468</v>
+        <v>2961381</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -32240,25 +32240,25 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>352.5</v>
+        <v>352.95</v>
       </c>
       <c r="D474" t="n">
-        <v>363.95</v>
+        <v>353.2</v>
       </c>
       <c r="E474" t="n">
-        <v>352.5</v>
+        <v>348.1</v>
       </c>
       <c r="F474" t="n">
-        <v>363.45</v>
+        <v>352.2</v>
       </c>
       <c r="G474" t="n">
-        <v>6249209</v>
+        <v>2687468</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -32267,25 +32267,25 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>355.95</v>
+        <v>352.5</v>
       </c>
       <c r="D475" t="n">
-        <v>361.65</v>
+        <v>363.95</v>
       </c>
       <c r="E475" t="n">
-        <v>354.4</v>
+        <v>352.5</v>
       </c>
       <c r="F475" t="n">
-        <v>358.4</v>
+        <v>363.45</v>
       </c>
       <c r="G475" t="n">
-        <v>3247810</v>
+        <v>6249209</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -32294,25 +32294,25 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>360.6</v>
+        <v>355.95</v>
       </c>
       <c r="D476" t="n">
-        <v>362.9</v>
+        <v>361.65</v>
       </c>
       <c r="E476" t="n">
-        <v>357.05</v>
+        <v>354.4</v>
       </c>
       <c r="F476" t="n">
-        <v>358.7</v>
+        <v>358.4</v>
       </c>
       <c r="G476" t="n">
-        <v>1869148</v>
+        <v>3247810</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -32321,25 +32321,25 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>354.05</v>
+        <v>360.6</v>
       </c>
       <c r="D477" t="n">
-        <v>354.75</v>
+        <v>362.9</v>
       </c>
       <c r="E477" t="n">
-        <v>344.35</v>
+        <v>357.05</v>
       </c>
       <c r="F477" t="n">
-        <v>349</v>
+        <v>358.7</v>
       </c>
       <c r="G477" t="n">
-        <v>7127278</v>
+        <v>1869148</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -32348,25 +32348,25 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>346.45</v>
+        <v>354.05</v>
       </c>
       <c r="D478" t="n">
-        <v>346.95</v>
+        <v>354.75</v>
       </c>
       <c r="E478" t="n">
-        <v>341</v>
+        <v>344.35</v>
       </c>
       <c r="F478" t="n">
-        <v>346.65</v>
+        <v>349</v>
       </c>
       <c r="G478" t="n">
-        <v>7334608</v>
+        <v>7127278</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -32375,25 +32375,25 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>345.05</v>
+        <v>346.45</v>
       </c>
       <c r="D479" t="n">
-        <v>348.95</v>
+        <v>346.95</v>
       </c>
       <c r="E479" t="n">
-        <v>340.95</v>
+        <v>341</v>
       </c>
       <c r="F479" t="n">
-        <v>340.95</v>
+        <v>346.65</v>
       </c>
       <c r="G479" t="n">
-        <v>5109676</v>
+        <v>7334608</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -32402,25 +32402,25 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>335</v>
+        <v>345.05</v>
       </c>
       <c r="D480" t="n">
-        <v>338.85</v>
+        <v>348.95</v>
       </c>
       <c r="E480" t="n">
-        <v>329.5</v>
+        <v>340.95</v>
       </c>
       <c r="F480" t="n">
-        <v>334.9</v>
+        <v>340.95</v>
       </c>
       <c r="G480" t="n">
-        <v>4672624</v>
+        <v>5109676</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -32429,25 +32429,25 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>334.9</v>
+        <v>335</v>
       </c>
       <c r="D481" t="n">
-        <v>334.9</v>
+        <v>338.85</v>
       </c>
       <c r="E481" t="n">
-        <v>334.9</v>
+        <v>329.5</v>
       </c>
       <c r="F481" t="n">
         <v>334.9</v>
       </c>
       <c r="G481" t="n">
-        <v>0</v>
+        <v>4672624</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -32456,52 +32456,52 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>335.9</v>
+        <v>334.9</v>
       </c>
       <c r="D482" t="n">
-        <v>344.1</v>
+        <v>334.9</v>
       </c>
       <c r="E482" t="n">
-        <v>334.3</v>
+        <v>334.9</v>
       </c>
       <c r="F482" t="n">
-        <v>340</v>
+        <v>334.9</v>
       </c>
       <c r="G482" t="n">
-        <v>5169746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>4389.8</v>
+        <v>335.9</v>
       </c>
       <c r="D483" t="n">
-        <v>4485</v>
+        <v>344.1</v>
       </c>
       <c r="E483" t="n">
-        <v>4361.9</v>
+        <v>334.3</v>
       </c>
       <c r="F483" t="n">
-        <v>4398.1</v>
+        <v>340</v>
       </c>
       <c r="G483" t="n">
-        <v>1347378</v>
+        <v>5169746</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -32510,25 +32510,25 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>4422</v>
+        <v>4389.8</v>
       </c>
       <c r="D484" t="n">
-        <v>4495</v>
+        <v>4485</v>
       </c>
       <c r="E484" t="n">
-        <v>4358</v>
+        <v>4361.9</v>
       </c>
       <c r="F484" t="n">
-        <v>4371.4</v>
+        <v>4398.1</v>
       </c>
       <c r="G484" t="n">
-        <v>902264</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -32537,25 +32537,25 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>4387.7</v>
+        <v>4422</v>
       </c>
       <c r="D485" t="n">
-        <v>4404</v>
+        <v>4495</v>
       </c>
       <c r="E485" t="n">
-        <v>4281.9</v>
+        <v>4358</v>
       </c>
       <c r="F485" t="n">
-        <v>4304.2</v>
+        <v>4371.4</v>
       </c>
       <c r="G485" t="n">
-        <v>463349</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -32564,25 +32564,25 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>4285</v>
+        <v>4387.7</v>
       </c>
       <c r="D486" t="n">
-        <v>4317</v>
+        <v>4404</v>
       </c>
       <c r="E486" t="n">
-        <v>4220</v>
+        <v>4281.9</v>
       </c>
       <c r="F486" t="n">
-        <v>4244.3</v>
+        <v>4304.2</v>
       </c>
       <c r="G486" t="n">
-        <v>398348</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -32591,25 +32591,25 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>4211</v>
+        <v>4285</v>
       </c>
       <c r="D487" t="n">
+        <v>4317</v>
+      </c>
+      <c r="E487" t="n">
         <v>4220</v>
       </c>
-      <c r="E487" t="n">
-        <v>4129.3</v>
-      </c>
       <c r="F487" t="n">
-        <v>4178.1</v>
+        <v>4244.3</v>
       </c>
       <c r="G487" t="n">
-        <v>470046</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32618,25 +32618,25 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>4190</v>
+        <v>4211</v>
       </c>
       <c r="D488" t="n">
-        <v>4324.4</v>
+        <v>4220</v>
       </c>
       <c r="E488" t="n">
-        <v>4190</v>
+        <v>4129.3</v>
       </c>
       <c r="F488" t="n">
-        <v>4257.3</v>
+        <v>4178.1</v>
       </c>
       <c r="G488" t="n">
-        <v>633457</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32645,25 +32645,25 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>4290</v>
+        <v>4190</v>
       </c>
       <c r="D489" t="n">
-        <v>4383</v>
+        <v>4324.4</v>
       </c>
       <c r="E489" t="n">
-        <v>4266</v>
+        <v>4190</v>
       </c>
       <c r="F489" t="n">
-        <v>4288.7</v>
+        <v>4257.3</v>
       </c>
       <c r="G489" t="n">
-        <v>835107</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32672,25 +32672,25 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>4299</v>
+        <v>4290</v>
       </c>
       <c r="D490" t="n">
-        <v>4340</v>
+        <v>4383</v>
       </c>
       <c r="E490" t="n">
-        <v>4216</v>
+        <v>4266</v>
       </c>
       <c r="F490" t="n">
-        <v>4243.8</v>
+        <v>4288.7</v>
       </c>
       <c r="G490" t="n">
-        <v>422024</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32699,25 +32699,25 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>4201.9</v>
+        <v>4299</v>
       </c>
       <c r="D491" t="n">
-        <v>4222</v>
+        <v>4340</v>
       </c>
       <c r="E491" t="n">
-        <v>4115</v>
+        <v>4216</v>
       </c>
       <c r="F491" t="n">
-        <v>4156</v>
+        <v>4243.8</v>
       </c>
       <c r="G491" t="n">
-        <v>378694</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32726,25 +32726,25 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>4181.8</v>
+        <v>4201.9</v>
       </c>
       <c r="D492" t="n">
-        <v>4385</v>
+        <v>4222</v>
       </c>
       <c r="E492" t="n">
-        <v>4129.4</v>
+        <v>4115</v>
       </c>
       <c r="F492" t="n">
-        <v>4362.2</v>
+        <v>4156</v>
       </c>
       <c r="G492" t="n">
-        <v>992864</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -32753,25 +32753,25 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>4380</v>
+        <v>4181.8</v>
       </c>
       <c r="D493" t="n">
-        <v>4478.3</v>
+        <v>4385</v>
       </c>
       <c r="E493" t="n">
-        <v>4280.1</v>
+        <v>4129.4</v>
       </c>
       <c r="F493" t="n">
-        <v>4395.7</v>
+        <v>4362.2</v>
       </c>
       <c r="G493" t="n">
-        <v>960643</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32780,25 +32780,25 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>4497.2</v>
+        <v>4380</v>
       </c>
       <c r="D494" t="n">
-        <v>4541.17</v>
+        <v>4478.3</v>
       </c>
       <c r="E494" t="n">
-        <v>4319.31</v>
+        <v>4280.1</v>
       </c>
       <c r="F494" t="n">
-        <v>4361.38</v>
+        <v>4395.7</v>
       </c>
       <c r="G494" t="n">
-        <v>1616021</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32807,25 +32807,25 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>4338</v>
+        <v>4497.2</v>
       </c>
       <c r="D495" t="n">
-        <v>4339.1</v>
+        <v>4541.17</v>
       </c>
       <c r="E495" t="n">
-        <v>4172.9</v>
+        <v>4319.31</v>
       </c>
       <c r="F495" t="n">
-        <v>4192.59</v>
+        <v>4361.38</v>
       </c>
       <c r="G495" t="n">
-        <v>648341</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32834,25 +32834,25 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>4297.32</v>
+        <v>4338</v>
       </c>
       <c r="D496" t="n">
-        <v>4595.14</v>
+        <v>4339.1</v>
       </c>
       <c r="E496" t="n">
-        <v>4249.35</v>
+        <v>4172.9</v>
       </c>
       <c r="F496" t="n">
-        <v>4521.18</v>
+        <v>4192.59</v>
       </c>
       <c r="G496" t="n">
-        <v>4510774</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32861,25 +32861,25 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>4557.56</v>
+        <v>4297.32</v>
       </c>
       <c r="D497" t="n">
-        <v>4737.05</v>
+        <v>4595.14</v>
       </c>
       <c r="E497" t="n">
-        <v>4537.17</v>
+        <v>4249.35</v>
       </c>
       <c r="F497" t="n">
-        <v>4583.14</v>
+        <v>4521.18</v>
       </c>
       <c r="G497" t="n">
-        <v>2334958</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32888,25 +32888,25 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>4606.13</v>
+        <v>4557.56</v>
       </c>
       <c r="D498" t="n">
-        <v>4777.02</v>
+        <v>4737.05</v>
       </c>
       <c r="E498" t="n">
-        <v>4590.24</v>
+        <v>4537.17</v>
       </c>
       <c r="F498" t="n">
-        <v>4759.23</v>
+        <v>4583.14</v>
       </c>
       <c r="G498" t="n">
-        <v>1899271</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32915,25 +32915,25 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>4817.7</v>
+        <v>4606.13</v>
       </c>
       <c r="D499" t="n">
-        <v>4929.93</v>
+        <v>4777.02</v>
       </c>
       <c r="E499" t="n">
-        <v>4722.06</v>
+        <v>4590.24</v>
       </c>
       <c r="F499" t="n">
-        <v>4890.75</v>
+        <v>4759.23</v>
       </c>
       <c r="G499" t="n">
-        <v>1924204</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32942,25 +32942,25 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>4896.95</v>
+        <v>4817.7</v>
       </c>
       <c r="D500" t="n">
-        <v>4976.9</v>
+        <v>4929.93</v>
       </c>
       <c r="E500" t="n">
-        <v>4780.02</v>
+        <v>4722.06</v>
       </c>
       <c r="F500" t="n">
-        <v>4813</v>
+        <v>4890.75</v>
       </c>
       <c r="G500" t="n">
-        <v>1117424</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32969,25 +32969,25 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>4790</v>
+        <v>4896.95</v>
       </c>
       <c r="D501" t="n">
-        <v>4968</v>
+        <v>4976.9</v>
       </c>
       <c r="E501" t="n">
-        <v>4780</v>
+        <v>4780.02</v>
       </c>
       <c r="F501" t="n">
-        <v>4939.2</v>
+        <v>4813</v>
       </c>
       <c r="G501" t="n">
-        <v>1296942</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32996,25 +32996,25 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4958</v>
+        <v>4790</v>
       </c>
       <c r="D502" t="n">
-        <v>5085</v>
+        <v>4968</v>
       </c>
       <c r="E502" t="n">
-        <v>4888.8</v>
+        <v>4780</v>
       </c>
       <c r="F502" t="n">
-        <v>4903</v>
+        <v>4939.2</v>
       </c>
       <c r="G502" t="n">
-        <v>1210476</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33023,25 +33023,25 @@
         </is>
       </c>
       <c r="C503" t="n">
+        <v>4958</v>
+      </c>
+      <c r="D503" t="n">
+        <v>5085</v>
+      </c>
+      <c r="E503" t="n">
+        <v>4888.8</v>
+      </c>
+      <c r="F503" t="n">
         <v>4903</v>
       </c>
-      <c r="D503" t="n">
-        <v>4940</v>
-      </c>
-      <c r="E503" t="n">
-        <v>4792.5</v>
-      </c>
-      <c r="F503" t="n">
-        <v>4859.8</v>
-      </c>
       <c r="G503" t="n">
-        <v>682980</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33050,25 +33050,25 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>4866</v>
+        <v>4903</v>
       </c>
       <c r="D504" t="n">
-        <v>4907.9</v>
+        <v>4940</v>
       </c>
       <c r="E504" t="n">
-        <v>4753</v>
+        <v>4792.5</v>
       </c>
       <c r="F504" t="n">
-        <v>4837.4</v>
+        <v>4859.8</v>
       </c>
       <c r="G504" t="n">
-        <v>613049</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -33077,25 +33077,25 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>4860</v>
+        <v>4866</v>
       </c>
       <c r="D505" t="n">
-        <v>5200</v>
+        <v>4907.9</v>
       </c>
       <c r="E505" t="n">
-        <v>4860</v>
+        <v>4753</v>
       </c>
       <c r="F505" t="n">
-        <v>5181</v>
+        <v>4837.4</v>
       </c>
       <c r="G505" t="n">
-        <v>3457670</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -33104,25 +33104,25 @@
         </is>
       </c>
       <c r="C506" t="n">
+        <v>4860</v>
+      </c>
+      <c r="D506" t="n">
         <v>5200</v>
       </c>
-      <c r="D506" t="n">
-        <v>5269</v>
-      </c>
       <c r="E506" t="n">
-        <v>4991.3</v>
+        <v>4860</v>
       </c>
       <c r="F506" t="n">
-        <v>5007.2</v>
+        <v>5181</v>
       </c>
       <c r="G506" t="n">
-        <v>1695255</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33131,25 +33131,25 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>5022</v>
+        <v>5200</v>
       </c>
       <c r="D507" t="n">
-        <v>5225</v>
+        <v>5269</v>
       </c>
       <c r="E507" t="n">
-        <v>5008.3</v>
+        <v>4991.3</v>
       </c>
       <c r="F507" t="n">
-        <v>5212.4</v>
+        <v>5007.2</v>
       </c>
       <c r="G507" t="n">
-        <v>1438746</v>
+        <v>1695255</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33158,25 +33158,25 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>5110</v>
+        <v>5022</v>
       </c>
       <c r="D508" t="n">
-        <v>5396.4</v>
+        <v>5225</v>
       </c>
       <c r="E508" t="n">
-        <v>5092.8</v>
+        <v>5008.3</v>
       </c>
       <c r="F508" t="n">
-        <v>5354.5</v>
+        <v>5212.4</v>
       </c>
       <c r="G508" t="n">
-        <v>2395703</v>
+        <v>1438746</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33185,25 +33185,25 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>5324.9</v>
+        <v>5110</v>
       </c>
       <c r="D509" t="n">
-        <v>5338</v>
+        <v>5396.4</v>
       </c>
       <c r="E509" t="n">
-        <v>5025</v>
+        <v>5092.8</v>
       </c>
       <c r="F509" t="n">
-        <v>5065</v>
+        <v>5354.5</v>
       </c>
       <c r="G509" t="n">
-        <v>1923210</v>
+        <v>2395703</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33212,25 +33212,25 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>5095.7</v>
+        <v>5324.9</v>
       </c>
       <c r="D510" t="n">
-        <v>5449.9</v>
+        <v>5338</v>
       </c>
       <c r="E510" t="n">
-        <v>5093</v>
+        <v>5025</v>
       </c>
       <c r="F510" t="n">
-        <v>5419.8</v>
+        <v>5065</v>
       </c>
       <c r="G510" t="n">
-        <v>4457308</v>
+        <v>1923210</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33239,25 +33239,25 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>5400</v>
+        <v>5095.7</v>
       </c>
       <c r="D511" t="n">
-        <v>5674.8</v>
+        <v>5449.9</v>
       </c>
       <c r="E511" t="n">
-        <v>5360</v>
+        <v>5093</v>
       </c>
       <c r="F511" t="n">
-        <v>5601</v>
+        <v>5419.8</v>
       </c>
       <c r="G511" t="n">
-        <v>4267482</v>
+        <v>4457308</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33266,25 +33266,25 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>5600</v>
+        <v>5400</v>
       </c>
       <c r="D512" t="n">
-        <v>5813</v>
+        <v>5674.8</v>
       </c>
       <c r="E512" t="n">
-        <v>5408.5</v>
+        <v>5360</v>
       </c>
       <c r="F512" t="n">
-        <v>5454.5</v>
+        <v>5601</v>
       </c>
       <c r="G512" t="n">
-        <v>2703933</v>
+        <v>4267482</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33293,25 +33293,25 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="D513" t="n">
-        <v>5413.2</v>
+        <v>5813</v>
       </c>
       <c r="E513" t="n">
-        <v>5191</v>
+        <v>5408.5</v>
       </c>
       <c r="F513" t="n">
-        <v>5273.5</v>
+        <v>5454.5</v>
       </c>
       <c r="G513" t="n">
-        <v>1906041</v>
+        <v>2703933</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33320,25 +33320,25 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>5323.1</v>
+        <v>5400</v>
       </c>
       <c r="D514" t="n">
-        <v>5465</v>
+        <v>5413.2</v>
       </c>
       <c r="E514" t="n">
-        <v>5231</v>
+        <v>5191</v>
       </c>
       <c r="F514" t="n">
-        <v>5271.9</v>
+        <v>5273.5</v>
       </c>
       <c r="G514" t="n">
-        <v>2623639</v>
+        <v>1906041</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33347,25 +33347,25 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>5380</v>
+        <v>5323.1</v>
       </c>
       <c r="D515" t="n">
-        <v>5450.1</v>
+        <v>5465</v>
       </c>
       <c r="E515" t="n">
-        <v>5250</v>
+        <v>5231</v>
       </c>
       <c r="F515" t="n">
-        <v>5272.2</v>
+        <v>5271.9</v>
       </c>
       <c r="G515" t="n">
-        <v>2077974</v>
+        <v>2623639</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33374,25 +33374,25 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>5344.9</v>
+        <v>5380</v>
       </c>
       <c r="D516" t="n">
-        <v>5450</v>
+        <v>5450.1</v>
       </c>
       <c r="E516" t="n">
-        <v>5290</v>
+        <v>5250</v>
       </c>
       <c r="F516" t="n">
-        <v>5322.9</v>
+        <v>5272.2</v>
       </c>
       <c r="G516" t="n">
-        <v>1962173</v>
+        <v>2077974</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -33401,25 +33401,25 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>5322</v>
+        <v>5344.9</v>
       </c>
       <c r="D517" t="n">
-        <v>5351.5</v>
+        <v>5450</v>
       </c>
       <c r="E517" t="n">
-        <v>5141</v>
+        <v>5290</v>
       </c>
       <c r="F517" t="n">
-        <v>5188.6</v>
+        <v>5322.9</v>
       </c>
       <c r="G517" t="n">
-        <v>1058849</v>
+        <v>1962173</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -33428,25 +33428,25 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>5215</v>
+        <v>5322</v>
       </c>
       <c r="D518" t="n">
-        <v>5315</v>
+        <v>5351.5</v>
       </c>
       <c r="E518" t="n">
-        <v>5117</v>
+        <v>5141</v>
       </c>
       <c r="F518" t="n">
-        <v>5136.5</v>
+        <v>5188.6</v>
       </c>
       <c r="G518" t="n">
-        <v>1421857</v>
+        <v>1058849</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -33455,25 +33455,25 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>5133</v>
+        <v>5215</v>
       </c>
       <c r="D519" t="n">
-        <v>5216.5</v>
+        <v>5315</v>
       </c>
       <c r="E519" t="n">
-        <v>5064</v>
+        <v>5117</v>
       </c>
       <c r="F519" t="n">
-        <v>5110</v>
+        <v>5136.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1273170</v>
+        <v>1421857</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -33482,25 +33482,25 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>5165</v>
+        <v>5133</v>
       </c>
       <c r="D520" t="n">
-        <v>5375</v>
+        <v>5216.5</v>
       </c>
       <c r="E520" t="n">
-        <v>5114</v>
+        <v>5064</v>
       </c>
       <c r="F520" t="n">
-        <v>5270</v>
+        <v>5110</v>
       </c>
       <c r="G520" t="n">
-        <v>2365927</v>
+        <v>1273170</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -33509,25 +33509,25 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>5297.5</v>
+        <v>5165</v>
       </c>
       <c r="D521" t="n">
-        <v>5424</v>
+        <v>5375</v>
       </c>
       <c r="E521" t="n">
-        <v>5164.5</v>
+        <v>5114</v>
       </c>
       <c r="F521" t="n">
-        <v>5193</v>
+        <v>5270</v>
       </c>
       <c r="G521" t="n">
-        <v>1816227</v>
+        <v>2365927</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -33536,25 +33536,25 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>5215</v>
+        <v>5297.5</v>
       </c>
       <c r="D522" t="n">
-        <v>5306.5</v>
+        <v>5424</v>
       </c>
       <c r="E522" t="n">
-        <v>5135</v>
+        <v>5164.5</v>
       </c>
       <c r="F522" t="n">
-        <v>5157</v>
+        <v>5193</v>
       </c>
       <c r="G522" t="n">
-        <v>975374</v>
+        <v>1816227</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -33563,25 +33563,25 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>5186</v>
+        <v>5215</v>
       </c>
       <c r="D523" t="n">
-        <v>5228.5</v>
+        <v>5306.5</v>
       </c>
       <c r="E523" t="n">
-        <v>5071.5</v>
+        <v>5135</v>
       </c>
       <c r="F523" t="n">
-        <v>5087.5</v>
+        <v>5157</v>
       </c>
       <c r="G523" t="n">
-        <v>812405</v>
+        <v>975374</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -33590,25 +33590,25 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>5100</v>
+        <v>5186</v>
       </c>
       <c r="D524" t="n">
-        <v>5127.5</v>
+        <v>5228.5</v>
       </c>
       <c r="E524" t="n">
-        <v>4881.5</v>
+        <v>5071.5</v>
       </c>
       <c r="F524" t="n">
-        <v>4898.5</v>
+        <v>5087.5</v>
       </c>
       <c r="G524" t="n">
-        <v>1696353</v>
+        <v>812405</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -33617,25 +33617,25 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>4910</v>
+        <v>5100</v>
       </c>
       <c r="D525" t="n">
-        <v>5054</v>
+        <v>5127.5</v>
       </c>
       <c r="E525" t="n">
-        <v>4900</v>
+        <v>4881.5</v>
       </c>
       <c r="F525" t="n">
-        <v>5013.5</v>
+        <v>4898.5</v>
       </c>
       <c r="G525" t="n">
-        <v>1532072</v>
+        <v>1696353</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -33644,25 +33644,25 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>4967.5</v>
+        <v>4910</v>
       </c>
       <c r="D526" t="n">
-        <v>5055</v>
+        <v>5054</v>
       </c>
       <c r="E526" t="n">
-        <v>4916</v>
+        <v>4900</v>
       </c>
       <c r="F526" t="n">
-        <v>5027</v>
+        <v>5013.5</v>
       </c>
       <c r="G526" t="n">
-        <v>870299</v>
+        <v>1532072</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -33671,25 +33671,25 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>5027</v>
+        <v>4967.5</v>
       </c>
       <c r="D527" t="n">
-        <v>5027</v>
+        <v>5055</v>
       </c>
       <c r="E527" t="n">
-        <v>5027</v>
+        <v>4916</v>
       </c>
       <c r="F527" t="n">
         <v>5027</v>
       </c>
       <c r="G527" t="n">
-        <v>0</v>
+        <v>870299</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -33698,25 +33698,25 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>4962</v>
+        <v>5027</v>
       </c>
       <c r="D528" t="n">
-        <v>4977.5</v>
+        <v>5027</v>
       </c>
       <c r="E528" t="n">
-        <v>4570</v>
+        <v>5027</v>
       </c>
       <c r="F528" t="n">
-        <v>4614</v>
+        <v>5027</v>
       </c>
       <c r="G528" t="n">
-        <v>1907037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -33725,25 +33725,25 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>4629.5</v>
+        <v>4962</v>
       </c>
       <c r="D529" t="n">
-        <v>4638.5</v>
+        <v>4977.5</v>
       </c>
       <c r="E529" t="n">
-        <v>4388</v>
+        <v>4570</v>
       </c>
       <c r="F529" t="n">
-        <v>4562</v>
+        <v>4614</v>
       </c>
       <c r="G529" t="n">
-        <v>1768403</v>
+        <v>1907037</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -33752,25 +33752,25 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>4563</v>
+        <v>4629.5</v>
       </c>
       <c r="D530" t="n">
-        <v>4618</v>
+        <v>4638.5</v>
       </c>
       <c r="E530" t="n">
-        <v>4484</v>
+        <v>4388</v>
       </c>
       <c r="F530" t="n">
-        <v>4578.5</v>
+        <v>4562</v>
       </c>
       <c r="G530" t="n">
-        <v>1120214</v>
+        <v>1768403</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -33779,25 +33779,25 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>4612</v>
+        <v>4563</v>
       </c>
       <c r="D531" t="n">
-        <v>4703.5</v>
+        <v>4618</v>
       </c>
       <c r="E531" t="n">
-        <v>4587</v>
+        <v>4484</v>
       </c>
       <c r="F531" t="n">
-        <v>4664.5</v>
+        <v>4578.5</v>
       </c>
       <c r="G531" t="n">
-        <v>1136499</v>
+        <v>1120214</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -33806,25 +33806,25 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>4683.5</v>
+        <v>4612</v>
       </c>
       <c r="D532" t="n">
-        <v>4744</v>
+        <v>4703.5</v>
       </c>
       <c r="E532" t="n">
-        <v>4610.5</v>
+        <v>4587</v>
       </c>
       <c r="F532" t="n">
-        <v>4718</v>
+        <v>4664.5</v>
       </c>
       <c r="G532" t="n">
-        <v>888237</v>
+        <v>1136499</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -33833,25 +33833,25 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>4768</v>
+        <v>4683.5</v>
       </c>
       <c r="D533" t="n">
-        <v>4835</v>
+        <v>4744</v>
       </c>
       <c r="E533" t="n">
-        <v>4742</v>
+        <v>4610.5</v>
       </c>
       <c r="F533" t="n">
-        <v>4817</v>
+        <v>4718</v>
       </c>
       <c r="G533" t="n">
-        <v>927925</v>
+        <v>888237</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -33860,25 +33860,25 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>4839.5</v>
+        <v>4768</v>
       </c>
       <c r="D534" t="n">
-        <v>4845</v>
+        <v>4835</v>
       </c>
       <c r="E534" t="n">
-        <v>4700</v>
+        <v>4742</v>
       </c>
       <c r="F534" t="n">
-        <v>4736</v>
+        <v>4817</v>
       </c>
       <c r="G534" t="n">
-        <v>549732</v>
+        <v>927925</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -33887,25 +33887,25 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>4685</v>
+        <v>4839.5</v>
       </c>
       <c r="D535" t="n">
-        <v>4719.5</v>
+        <v>4845</v>
       </c>
       <c r="E535" t="n">
-        <v>4633</v>
+        <v>4700</v>
       </c>
       <c r="F535" t="n">
-        <v>4661.5</v>
+        <v>4736</v>
       </c>
       <c r="G535" t="n">
-        <v>501756</v>
+        <v>549732</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -33914,25 +33914,25 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>4675</v>
+        <v>4685</v>
       </c>
       <c r="D536" t="n">
-        <v>4710</v>
+        <v>4719.5</v>
       </c>
       <c r="E536" t="n">
-        <v>4522</v>
+        <v>4633</v>
       </c>
       <c r="F536" t="n">
-        <v>4545</v>
+        <v>4661.5</v>
       </c>
       <c r="G536" t="n">
-        <v>696170</v>
+        <v>501756</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -33941,25 +33941,25 @@
         </is>
       </c>
       <c r="C537" t="n">
+        <v>4675</v>
+      </c>
+      <c r="D537" t="n">
+        <v>4710</v>
+      </c>
+      <c r="E537" t="n">
+        <v>4522</v>
+      </c>
+      <c r="F537" t="n">
         <v>4545</v>
       </c>
-      <c r="D537" t="n">
-        <v>4595</v>
-      </c>
-      <c r="E537" t="n">
-        <v>4456</v>
-      </c>
-      <c r="F537" t="n">
-        <v>4566.5</v>
-      </c>
       <c r="G537" t="n">
-        <v>657592</v>
+        <v>696170</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -33968,25 +33968,25 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>4550</v>
+        <v>4545</v>
       </c>
       <c r="D538" t="n">
-        <v>4664</v>
+        <v>4595</v>
       </c>
       <c r="E538" t="n">
-        <v>4453</v>
+        <v>4456</v>
       </c>
       <c r="F538" t="n">
-        <v>4613</v>
+        <v>4566.5</v>
       </c>
       <c r="G538" t="n">
-        <v>822138</v>
+        <v>657592</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -33995,25 +33995,25 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>4625</v>
+        <v>4550</v>
       </c>
       <c r="D539" t="n">
-        <v>4684.5</v>
+        <v>4664</v>
       </c>
       <c r="E539" t="n">
-        <v>4530</v>
+        <v>4453</v>
       </c>
       <c r="F539" t="n">
-        <v>4548</v>
+        <v>4613</v>
       </c>
       <c r="G539" t="n">
-        <v>586472</v>
+        <v>822138</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -34022,25 +34022,25 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>4545</v>
+        <v>4625</v>
       </c>
       <c r="D540" t="n">
-        <v>4620</v>
+        <v>4684.5</v>
       </c>
       <c r="E540" t="n">
-        <v>4463.8</v>
+        <v>4530</v>
       </c>
       <c r="F540" t="n">
-        <v>4520.3</v>
+        <v>4548</v>
       </c>
       <c r="G540" t="n">
-        <v>752580</v>
+        <v>586472</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -34049,25 +34049,25 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>4520.3</v>
+        <v>4545</v>
       </c>
       <c r="D541" t="n">
-        <v>4520.3</v>
+        <v>4620</v>
       </c>
       <c r="E541" t="n">
-        <v>4520.3</v>
+        <v>4463.8</v>
       </c>
       <c r="F541" t="n">
         <v>4520.3</v>
       </c>
       <c r="G541" t="n">
-        <v>0</v>
+        <v>752580</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -34076,52 +34076,52 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>4543</v>
+        <v>4520.3</v>
       </c>
       <c r="D542" t="n">
-        <v>4790</v>
+        <v>4520.3</v>
       </c>
       <c r="E542" t="n">
-        <v>4535</v>
+        <v>4520.3</v>
       </c>
       <c r="F542" t="n">
-        <v>4765.1</v>
+        <v>4520.3</v>
       </c>
       <c r="G542" t="n">
-        <v>1646842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>1417</v>
+        <v>4543</v>
       </c>
       <c r="D543" t="n">
-        <v>1436</v>
+        <v>4790</v>
       </c>
       <c r="E543" t="n">
-        <v>1410.1</v>
+        <v>4535</v>
       </c>
       <c r="F543" t="n">
-        <v>1423.9</v>
+        <v>4765.1</v>
       </c>
       <c r="G543" t="n">
-        <v>623969</v>
+        <v>1646842</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -34130,25 +34130,25 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>1428</v>
+        <v>1417</v>
       </c>
       <c r="D544" t="n">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="E544" t="n">
-        <v>1351.5</v>
+        <v>1410.1</v>
       </c>
       <c r="F544" t="n">
-        <v>1359.1</v>
+        <v>1423.9</v>
       </c>
       <c r="G544" t="n">
-        <v>808190</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -34157,25 +34157,25 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>1349.8</v>
+        <v>1428</v>
       </c>
       <c r="D545" t="n">
-        <v>1357.8</v>
+        <v>1428</v>
       </c>
       <c r="E545" t="n">
-        <v>1330.1</v>
+        <v>1351.5</v>
       </c>
       <c r="F545" t="n">
-        <v>1340.8</v>
+        <v>1359.1</v>
       </c>
       <c r="G545" t="n">
-        <v>345535</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -34184,25 +34184,25 @@
         </is>
       </c>
       <c r="C546" t="n">
+        <v>1349.8</v>
+      </c>
+      <c r="D546" t="n">
+        <v>1357.8</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="F546" t="n">
         <v>1340.8</v>
       </c>
-      <c r="D546" t="n">
-        <v>1387.7</v>
-      </c>
-      <c r="E546" t="n">
-        <v>1316</v>
-      </c>
-      <c r="F546" t="n">
-        <v>1374.4</v>
-      </c>
       <c r="G546" t="n">
-        <v>974660</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -34211,25 +34211,25 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>1372.9</v>
+        <v>1340.8</v>
       </c>
       <c r="D547" t="n">
-        <v>1390</v>
+        <v>1387.7</v>
       </c>
       <c r="E547" t="n">
-        <v>1355.1</v>
+        <v>1316</v>
       </c>
       <c r="F547" t="n">
-        <v>1363.5</v>
+        <v>1374.4</v>
       </c>
       <c r="G547" t="n">
-        <v>479123</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -34238,25 +34238,25 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>1363</v>
+        <v>1372.9</v>
       </c>
       <c r="D548" t="n">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E548" t="n">
         <v>1355.1</v>
       </c>
       <c r="F548" t="n">
-        <v>1380</v>
+        <v>1363.5</v>
       </c>
       <c r="G548" t="n">
-        <v>616767</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -34265,25 +34265,25 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="D549" t="n">
-        <v>1368</v>
+        <v>1392</v>
       </c>
       <c r="E549" t="n">
-        <v>1272.1</v>
+        <v>1355.1</v>
       </c>
       <c r="F549" t="n">
-        <v>1288.3</v>
+        <v>1380</v>
       </c>
       <c r="G549" t="n">
-        <v>1098492</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -34292,25 +34292,25 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="D550" t="n">
-        <v>1318.5</v>
+        <v>1368</v>
       </c>
       <c r="E550" t="n">
-        <v>1257</v>
+        <v>1272.1</v>
       </c>
       <c r="F550" t="n">
-        <v>1316.2</v>
+        <v>1288.3</v>
       </c>
       <c r="G550" t="n">
-        <v>1172726</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -34319,25 +34319,25 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>1317.7</v>
+        <v>1300</v>
       </c>
       <c r="D551" t="n">
-        <v>1319.8</v>
+        <v>1318.5</v>
       </c>
       <c r="E551" t="n">
-        <v>1270.5</v>
+        <v>1257</v>
       </c>
       <c r="F551" t="n">
-        <v>1306</v>
+        <v>1316.2</v>
       </c>
       <c r="G551" t="n">
-        <v>832973</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -34346,25 +34346,25 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>1319.9</v>
+        <v>1317.7</v>
       </c>
       <c r="D552" t="n">
-        <v>1355.4</v>
+        <v>1319.8</v>
       </c>
       <c r="E552" t="n">
-        <v>1308</v>
+        <v>1270.5</v>
       </c>
       <c r="F552" t="n">
-        <v>1343.4</v>
+        <v>1306</v>
       </c>
       <c r="G552" t="n">
-        <v>1287698</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -34373,25 +34373,25 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>1379</v>
+        <v>1319.9</v>
       </c>
       <c r="D553" t="n">
-        <v>1468</v>
+        <v>1355.4</v>
       </c>
       <c r="E553" t="n">
-        <v>1361</v>
+        <v>1308</v>
       </c>
       <c r="F553" t="n">
-        <v>1377.8</v>
+        <v>1343.4</v>
       </c>
       <c r="G553" t="n">
-        <v>9950655</v>
+        <v>1287698</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -34400,25 +34400,25 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>1380.5</v>
+        <v>1379</v>
       </c>
       <c r="D554" t="n">
-        <v>1403.3</v>
+        <v>1468</v>
       </c>
       <c r="E554" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F554" t="n">
-        <v>1366.8</v>
+        <v>1377.8</v>
       </c>
       <c r="G554" t="n">
-        <v>1567542</v>
+        <v>9950655</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -34427,25 +34427,25 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>1380</v>
+        <v>1380.5</v>
       </c>
       <c r="D555" t="n">
-        <v>1397.5</v>
+        <v>1403.3</v>
       </c>
       <c r="E555" t="n">
-        <v>1351.6</v>
+        <v>1363</v>
       </c>
       <c r="F555" t="n">
-        <v>1360.6</v>
+        <v>1366.8</v>
       </c>
       <c r="G555" t="n">
-        <v>1098353</v>
+        <v>1567542</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -34454,25 +34454,25 @@
         </is>
       </c>
       <c r="C556" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D556" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F556" t="n">
         <v>1360.6</v>
       </c>
-      <c r="D556" t="n">
-        <v>1428</v>
-      </c>
-      <c r="E556" t="n">
-        <v>1354.5</v>
-      </c>
-      <c r="F556" t="n">
-        <v>1421.6</v>
-      </c>
       <c r="G556" t="n">
-        <v>2055261</v>
+        <v>1098353</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -34481,25 +34481,25 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>1428.14</v>
+        <v>1360.6</v>
       </c>
       <c r="D557" t="n">
-        <v>1451.52</v>
+        <v>1428</v>
       </c>
       <c r="E557" t="n">
-        <v>1417.55</v>
+        <v>1354.5</v>
       </c>
       <c r="F557" t="n">
-        <v>1432.63</v>
+        <v>1421.6</v>
       </c>
       <c r="G557" t="n">
-        <v>1243415</v>
+        <v>2055261</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -34508,25 +34508,25 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>1432.53</v>
+        <v>1428.14</v>
       </c>
       <c r="D558" t="n">
-        <v>1458.51</v>
+        <v>1451.52</v>
       </c>
       <c r="E558" t="n">
-        <v>1403.56</v>
+        <v>1417.55</v>
       </c>
       <c r="F558" t="n">
-        <v>1416.55</v>
+        <v>1432.63</v>
       </c>
       <c r="G558" t="n">
-        <v>1123973</v>
+        <v>1243415</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -34535,25 +34535,25 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>1412.46</v>
+        <v>1432.53</v>
       </c>
       <c r="D559" t="n">
-        <v>1432.53</v>
+        <v>1458.51</v>
       </c>
       <c r="E559" t="n">
-        <v>1406.06</v>
+        <v>1403.56</v>
       </c>
       <c r="F559" t="n">
-        <v>1423.24</v>
+        <v>1416.55</v>
       </c>
       <c r="G559" t="n">
-        <v>509551</v>
+        <v>1123973</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -34562,25 +34562,25 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>1432.63</v>
+        <v>1412.46</v>
       </c>
       <c r="D560" t="n">
-        <v>1520.44</v>
+        <v>1432.53</v>
       </c>
       <c r="E560" t="n">
-        <v>1426.04</v>
+        <v>1406.06</v>
       </c>
       <c r="F560" t="n">
-        <v>1514.85</v>
+        <v>1423.24</v>
       </c>
       <c r="G560" t="n">
-        <v>3863757</v>
+        <v>509551</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -34589,25 +34589,25 @@
         </is>
       </c>
       <c r="C561" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="D561" t="n">
+        <v>1520.44</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1426.04</v>
+      </c>
+      <c r="F561" t="n">
         <v>1514.85</v>
       </c>
-      <c r="D561" t="n">
-        <v>1541.42</v>
-      </c>
-      <c r="E561" t="n">
-        <v>1485.38</v>
-      </c>
-      <c r="F561" t="n">
-        <v>1493.27</v>
-      </c>
       <c r="G561" t="n">
-        <v>1508375</v>
+        <v>3863757</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -34616,25 +34616,25 @@
         </is>
       </c>
       <c r="C562" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="D562" t="n">
+        <v>1541.42</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1485.38</v>
+      </c>
+      <c r="F562" t="n">
         <v>1493.27</v>
       </c>
-      <c r="D562" t="n">
-        <v>1512.45</v>
-      </c>
-      <c r="E562" t="n">
-        <v>1463.6</v>
-      </c>
-      <c r="F562" t="n">
-        <v>1471.79</v>
-      </c>
       <c r="G562" t="n">
-        <v>749197</v>
+        <v>1508375</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -34643,25 +34643,25 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>1480.39</v>
+        <v>1493.27</v>
       </c>
       <c r="D563" t="n">
-        <v>1498.97</v>
+        <v>1512.45</v>
       </c>
       <c r="E563" t="n">
-        <v>1449.52</v>
+        <v>1463.6</v>
       </c>
       <c r="F563" t="n">
-        <v>1466.2</v>
+        <v>1471.79</v>
       </c>
       <c r="G563" t="n">
-        <v>742118</v>
+        <v>749197</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -34670,25 +34670,25 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>1478.49</v>
+        <v>1480.39</v>
       </c>
       <c r="D564" t="n">
-        <v>1505.16</v>
+        <v>1498.97</v>
       </c>
       <c r="E564" t="n">
-        <v>1450.52</v>
+        <v>1449.52</v>
       </c>
       <c r="F564" t="n">
-        <v>1463.7</v>
+        <v>1466.2</v>
       </c>
       <c r="G564" t="n">
-        <v>811337</v>
+        <v>742118</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -34697,25 +34697,25 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>1475.79</v>
+        <v>1478.49</v>
       </c>
       <c r="D565" t="n">
-        <v>1502.06</v>
+        <v>1505.16</v>
       </c>
       <c r="E565" t="n">
-        <v>1457.01</v>
+        <v>1450.52</v>
       </c>
       <c r="F565" t="n">
-        <v>1466.4</v>
+        <v>1463.7</v>
       </c>
       <c r="G565" t="n">
-        <v>972670</v>
+        <v>811337</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -34724,25 +34724,25 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>1489.9</v>
+        <v>1475.79</v>
       </c>
       <c r="D566" t="n">
-        <v>1521</v>
+        <v>1502.06</v>
       </c>
       <c r="E566" t="n">
-        <v>1488.9</v>
+        <v>1457.01</v>
       </c>
       <c r="F566" t="n">
-        <v>1500.1</v>
+        <v>1466.4</v>
       </c>
       <c r="G566" t="n">
-        <v>2323890</v>
+        <v>972670</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -34751,25 +34751,25 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>1507.9</v>
+        <v>1489.9</v>
       </c>
       <c r="D567" t="n">
-        <v>1514.6</v>
+        <v>1521</v>
       </c>
       <c r="E567" t="n">
-        <v>1475</v>
+        <v>1488.9</v>
       </c>
       <c r="F567" t="n">
-        <v>1494.8</v>
+        <v>1500.1</v>
       </c>
       <c r="G567" t="n">
-        <v>901426</v>
+        <v>2323890</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -34778,25 +34778,25 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>1504.8</v>
+        <v>1507.9</v>
       </c>
       <c r="D568" t="n">
-        <v>1525.8</v>
+        <v>1514.6</v>
       </c>
       <c r="E568" t="n">
-        <v>1415.7</v>
+        <v>1475</v>
       </c>
       <c r="F568" t="n">
-        <v>1443.7</v>
+        <v>1494.8</v>
       </c>
       <c r="G568" t="n">
-        <v>1342162</v>
+        <v>901426</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -34805,25 +34805,25 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>1445</v>
+        <v>1504.8</v>
       </c>
       <c r="D569" t="n">
-        <v>1449</v>
+        <v>1525.8</v>
       </c>
       <c r="E569" t="n">
-        <v>1421.1</v>
+        <v>1415.7</v>
       </c>
       <c r="F569" t="n">
-        <v>1439.3</v>
+        <v>1443.7</v>
       </c>
       <c r="G569" t="n">
-        <v>603250</v>
+        <v>1342162</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -34832,25 +34832,25 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="D570" t="n">
-        <v>1472</v>
+        <v>1449</v>
       </c>
       <c r="E570" t="n">
-        <v>1441</v>
+        <v>1421.1</v>
       </c>
       <c r="F570" t="n">
-        <v>1459.9</v>
+        <v>1439.3</v>
       </c>
       <c r="G570" t="n">
-        <v>758782</v>
+        <v>603250</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -34859,25 +34859,25 @@
         </is>
       </c>
       <c r="C571" t="n">
+        <v>1454</v>
+      </c>
+      <c r="D571" t="n">
+        <v>1472</v>
+      </c>
+      <c r="E571" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F571" t="n">
         <v>1459.9</v>
       </c>
-      <c r="D571" t="n">
-        <v>1467.6</v>
-      </c>
-      <c r="E571" t="n">
-        <v>1442</v>
-      </c>
-      <c r="F571" t="n">
-        <v>1458.1</v>
-      </c>
       <c r="G571" t="n">
-        <v>522653</v>
+        <v>758782</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -34886,25 +34886,25 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>1466</v>
+        <v>1459.9</v>
       </c>
       <c r="D572" t="n">
-        <v>1483</v>
+        <v>1467.6</v>
       </c>
       <c r="E572" t="n">
-        <v>1457.8</v>
+        <v>1442</v>
       </c>
       <c r="F572" t="n">
-        <v>1474.1</v>
+        <v>1458.1</v>
       </c>
       <c r="G572" t="n">
-        <v>708242</v>
+        <v>522653</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -34913,25 +34913,25 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="D573" t="n">
-        <v>1499</v>
+        <v>1483</v>
       </c>
       <c r="E573" t="n">
-        <v>1467.1</v>
+        <v>1457.8</v>
       </c>
       <c r="F573" t="n">
-        <v>1493.5</v>
+        <v>1474.1</v>
       </c>
       <c r="G573" t="n">
-        <v>957727</v>
+        <v>708242</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -34940,25 +34940,25 @@
         </is>
       </c>
       <c r="C574" t="n">
+        <v>1471</v>
+      </c>
+      <c r="D574" t="n">
         <v>1499</v>
       </c>
-      <c r="D574" t="n">
-        <v>1505</v>
-      </c>
       <c r="E574" t="n">
-        <v>1470</v>
+        <v>1467.1</v>
       </c>
       <c r="F574" t="n">
-        <v>1474.3</v>
+        <v>1493.5</v>
       </c>
       <c r="G574" t="n">
-        <v>404693</v>
+        <v>957727</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -34967,25 +34967,25 @@
         </is>
       </c>
       <c r="C575" t="n">
+        <v>1499</v>
+      </c>
+      <c r="D575" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E575" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F575" t="n">
         <v>1474.3</v>
       </c>
-      <c r="D575" t="n">
-        <v>1474.3</v>
-      </c>
-      <c r="E575" t="n">
-        <v>1392.6</v>
-      </c>
-      <c r="F575" t="n">
-        <v>1437</v>
-      </c>
       <c r="G575" t="n">
-        <v>1596920</v>
+        <v>404693</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -34994,25 +34994,25 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>1435</v>
+        <v>1474.3</v>
       </c>
       <c r="D576" t="n">
-        <v>1459</v>
+        <v>1474.3</v>
       </c>
       <c r="E576" t="n">
-        <v>1418.7</v>
+        <v>1392.6</v>
       </c>
       <c r="F576" t="n">
-        <v>1447.9</v>
+        <v>1437</v>
       </c>
       <c r="G576" t="n">
-        <v>608516</v>
+        <v>1596920</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -35021,25 +35021,25 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>1439.5</v>
+        <v>1435</v>
       </c>
       <c r="D577" t="n">
-        <v>1457.5</v>
+        <v>1459</v>
       </c>
       <c r="E577" t="n">
-        <v>1427.7</v>
+        <v>1418.7</v>
       </c>
       <c r="F577" t="n">
-        <v>1434</v>
+        <v>1447.9</v>
       </c>
       <c r="G577" t="n">
-        <v>785469</v>
+        <v>608516</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -35048,25 +35048,25 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>1447.3</v>
+        <v>1439.5</v>
       </c>
       <c r="D578" t="n">
-        <v>1460</v>
+        <v>1457.5</v>
       </c>
       <c r="E578" t="n">
-        <v>1405.5</v>
+        <v>1427.7</v>
       </c>
       <c r="F578" t="n">
-        <v>1452.8</v>
+        <v>1434</v>
       </c>
       <c r="G578" t="n">
-        <v>566330</v>
+        <v>785469</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -35075,25 +35075,25 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>1455.2</v>
+        <v>1447.3</v>
       </c>
       <c r="D579" t="n">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="E579" t="n">
-        <v>1450.4</v>
+        <v>1405.5</v>
       </c>
       <c r="F579" t="n">
-        <v>1457.3</v>
+        <v>1452.8</v>
       </c>
       <c r="G579" t="n">
-        <v>569018</v>
+        <v>566330</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -35102,25 +35102,25 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>1458.5</v>
+        <v>1455.2</v>
       </c>
       <c r="D580" t="n">
-        <v>1645</v>
+        <v>1470</v>
       </c>
       <c r="E580" t="n">
-        <v>1458.3</v>
+        <v>1450.4</v>
       </c>
       <c r="F580" t="n">
-        <v>1634.8</v>
+        <v>1457.3</v>
       </c>
       <c r="G580" t="n">
-        <v>13079561</v>
+        <v>569018</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -35129,25 +35129,25 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>1627</v>
+        <v>1458.5</v>
       </c>
       <c r="D581" t="n">
-        <v>1660</v>
+        <v>1645</v>
       </c>
       <c r="E581" t="n">
-        <v>1592.2</v>
+        <v>1458.3</v>
       </c>
       <c r="F581" t="n">
-        <v>1639.2</v>
+        <v>1634.8</v>
       </c>
       <c r="G581" t="n">
-        <v>2823789</v>
+        <v>13079561</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -35156,25 +35156,25 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>1639</v>
+        <v>1627</v>
       </c>
       <c r="D582" t="n">
         <v>1660</v>
       </c>
       <c r="E582" t="n">
-        <v>1616</v>
+        <v>1592.2</v>
       </c>
       <c r="F582" t="n">
-        <v>1622.4</v>
+        <v>1639.2</v>
       </c>
       <c r="G582" t="n">
-        <v>1096481</v>
+        <v>2823789</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -35183,25 +35183,25 @@
         </is>
       </c>
       <c r="C583" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D583" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E583" t="n">
         <v>1616</v>
       </c>
-      <c r="D583" t="n">
-        <v>1639.9</v>
-      </c>
-      <c r="E583" t="n">
-        <v>1594</v>
-      </c>
       <c r="F583" t="n">
-        <v>1598.8</v>
+        <v>1622.4</v>
       </c>
       <c r="G583" t="n">
-        <v>738911</v>
+        <v>1096481</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -35210,25 +35210,25 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>1598.9</v>
+        <v>1616</v>
       </c>
       <c r="D584" t="n">
-        <v>1608.2</v>
+        <v>1639.9</v>
       </c>
       <c r="E584" t="n">
-        <v>1556.1</v>
+        <v>1594</v>
       </c>
       <c r="F584" t="n">
-        <v>1589.3</v>
+        <v>1598.8</v>
       </c>
       <c r="G584" t="n">
-        <v>638884</v>
+        <v>738911</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -35237,25 +35237,25 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>1589.3</v>
+        <v>1598.9</v>
       </c>
       <c r="D585" t="n">
-        <v>1589.3</v>
+        <v>1608.2</v>
       </c>
       <c r="E585" t="n">
-        <v>1589.3</v>
+        <v>1556.1</v>
       </c>
       <c r="F585" t="n">
         <v>1589.3</v>
       </c>
       <c r="G585" t="n">
-        <v>0</v>
+        <v>638884</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -35264,25 +35264,25 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>1613.7</v>
+        <v>1589.3</v>
       </c>
       <c r="D586" t="n">
-        <v>1614</v>
+        <v>1589.3</v>
       </c>
       <c r="E586" t="n">
-        <v>1500.3</v>
+        <v>1589.3</v>
       </c>
       <c r="F586" t="n">
-        <v>1507.7</v>
+        <v>1589.3</v>
       </c>
       <c r="G586" t="n">
-        <v>1180574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -35291,25 +35291,25 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>1508.9</v>
+        <v>1613.7</v>
       </c>
       <c r="D587" t="n">
-        <v>1522.8</v>
+        <v>1614</v>
       </c>
       <c r="E587" t="n">
-        <v>1418</v>
+        <v>1500.3</v>
       </c>
       <c r="F587" t="n">
-        <v>1511.2</v>
+        <v>1507.7</v>
       </c>
       <c r="G587" t="n">
-        <v>1682259</v>
+        <v>1180574</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -35318,25 +35318,25 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>1513.5</v>
+        <v>1508.9</v>
       </c>
       <c r="D588" t="n">
-        <v>1658</v>
+        <v>1522.8</v>
       </c>
       <c r="E588" t="n">
-        <v>1513.5</v>
+        <v>1418</v>
       </c>
       <c r="F588" t="n">
-        <v>1617.7</v>
+        <v>1511.2</v>
       </c>
       <c r="G588" t="n">
-        <v>9182371</v>
+        <v>1682259</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -35345,25 +35345,25 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>1614.1</v>
+        <v>1513.5</v>
       </c>
       <c r="D589" t="n">
-        <v>1764</v>
+        <v>1658</v>
       </c>
       <c r="E589" t="n">
-        <v>1612</v>
+        <v>1513.5</v>
       </c>
       <c r="F589" t="n">
-        <v>1728.9</v>
+        <v>1617.7</v>
       </c>
       <c r="G589" t="n">
-        <v>10474149</v>
+        <v>9182371</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -35372,25 +35372,25 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>1721</v>
+        <v>1614.1</v>
       </c>
       <c r="D590" t="n">
-        <v>1727.4</v>
+        <v>1764</v>
       </c>
       <c r="E590" t="n">
-        <v>1658</v>
+        <v>1612</v>
       </c>
       <c r="F590" t="n">
-        <v>1713.3</v>
+        <v>1728.9</v>
       </c>
       <c r="G590" t="n">
-        <v>1838433</v>
+        <v>10474149</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -35399,25 +35399,25 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D591" t="n">
-        <v>1803.9</v>
+        <v>1727.4</v>
       </c>
       <c r="E591" t="n">
-        <v>1714.5</v>
+        <v>1658</v>
       </c>
       <c r="F591" t="n">
-        <v>1741.8</v>
+        <v>1713.3</v>
       </c>
       <c r="G591" t="n">
-        <v>4023734</v>
+        <v>1838433</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -35426,25 +35426,25 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>1750.3</v>
+        <v>1720</v>
       </c>
       <c r="D592" t="n">
-        <v>1750.3</v>
+        <v>1803.9</v>
       </c>
       <c r="E592" t="n">
-        <v>1702.1</v>
+        <v>1714.5</v>
       </c>
       <c r="F592" t="n">
-        <v>1719.4</v>
+        <v>1741.8</v>
       </c>
       <c r="G592" t="n">
-        <v>1400218</v>
+        <v>4023734</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -35453,25 +35453,25 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1699.9</v>
+        <v>1750.3</v>
       </c>
       <c r="D593" t="n">
-        <v>1737.2</v>
+        <v>1750.3</v>
       </c>
       <c r="E593" t="n">
-        <v>1686.1</v>
+        <v>1702.1</v>
       </c>
       <c r="F593" t="n">
-        <v>1698.6</v>
+        <v>1719.4</v>
       </c>
       <c r="G593" t="n">
-        <v>841054</v>
+        <v>1400218</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -35480,25 +35480,25 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>1703</v>
+        <v>1699.9</v>
       </c>
       <c r="D594" t="n">
-        <v>1742.7</v>
+        <v>1737.2</v>
       </c>
       <c r="E594" t="n">
-        <v>1702</v>
+        <v>1686.1</v>
       </c>
       <c r="F594" t="n">
-        <v>1732.6</v>
+        <v>1698.6</v>
       </c>
       <c r="G594" t="n">
-        <v>1026235</v>
+        <v>841054</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -35507,25 +35507,25 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>1733.3</v>
+        <v>1703</v>
       </c>
       <c r="D595" t="n">
-        <v>1781.9</v>
+        <v>1742.7</v>
       </c>
       <c r="E595" t="n">
-        <v>1723.9</v>
+        <v>1702</v>
       </c>
       <c r="F595" t="n">
-        <v>1746.4</v>
+        <v>1732.6</v>
       </c>
       <c r="G595" t="n">
-        <v>1859395</v>
+        <v>1026235</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -35534,25 +35534,25 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>1745</v>
+        <v>1733.3</v>
       </c>
       <c r="D596" t="n">
+        <v>1781.9</v>
+      </c>
+      <c r="E596" t="n">
+        <v>1723.9</v>
+      </c>
+      <c r="F596" t="n">
         <v>1746.4</v>
       </c>
-      <c r="E596" t="n">
-        <v>1685</v>
-      </c>
-      <c r="F596" t="n">
-        <v>1692.6</v>
-      </c>
       <c r="G596" t="n">
-        <v>1111808</v>
+        <v>1859395</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -35561,25 +35561,25 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>1686</v>
+        <v>1745</v>
       </c>
       <c r="D597" t="n">
-        <v>1820</v>
+        <v>1746.4</v>
       </c>
       <c r="E597" t="n">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="F597" t="n">
-        <v>1782.9</v>
+        <v>1692.6</v>
       </c>
       <c r="G597" t="n">
-        <v>3788979</v>
+        <v>1111808</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -35588,79 +35588,79 @@
         </is>
       </c>
       <c r="C598" t="n">
+        <v>1686</v>
+      </c>
+      <c r="D598" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E598" t="n">
+        <v>1686</v>
+      </c>
+      <c r="F598" t="n">
         <v>1782.9</v>
       </c>
-      <c r="D598" t="n">
-        <v>1822.6</v>
-      </c>
-      <c r="E598" t="n">
-        <v>1710.1</v>
-      </c>
-      <c r="F598" t="n">
-        <v>1717.9</v>
-      </c>
       <c r="G598" t="n">
-        <v>1874242</v>
+        <v>3788979</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>728.75</v>
+        <v>1782.9</v>
       </c>
       <c r="D599" t="n">
-        <v>729.05</v>
+        <v>1822.6</v>
       </c>
       <c r="E599" t="n">
-        <v>680</v>
+        <v>1710.1</v>
       </c>
       <c r="F599" t="n">
-        <v>696</v>
+        <v>1717.9</v>
       </c>
       <c r="G599" t="n">
-        <v>4260675</v>
+        <v>1874242</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>701.4</v>
+        <v>1739.7</v>
       </c>
       <c r="D600" t="n">
-        <v>723.8</v>
+        <v>1757.7</v>
       </c>
       <c r="E600" t="n">
-        <v>691.55</v>
+        <v>1692.3</v>
       </c>
       <c r="F600" t="n">
-        <v>722.1</v>
+        <v>1700.4</v>
       </c>
       <c r="G600" t="n">
-        <v>2030402</v>
+        <v>846292</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -35669,25 +35669,25 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>726</v>
+        <v>728.75</v>
       </c>
       <c r="D601" t="n">
-        <v>770</v>
+        <v>729.05</v>
       </c>
       <c r="E601" t="n">
-        <v>725.15</v>
+        <v>680</v>
       </c>
       <c r="F601" t="n">
-        <v>763.75</v>
+        <v>696</v>
       </c>
       <c r="G601" t="n">
-        <v>3139171</v>
+        <v>4260675</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -35696,25 +35696,25 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>740</v>
+        <v>701.4</v>
       </c>
       <c r="D602" t="n">
-        <v>759.6</v>
+        <v>723.8</v>
       </c>
       <c r="E602" t="n">
-        <v>736.05</v>
+        <v>691.55</v>
       </c>
       <c r="F602" t="n">
-        <v>747.3</v>
+        <v>722.1</v>
       </c>
       <c r="G602" t="n">
-        <v>1983807</v>
+        <v>2030402</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -35723,25 +35723,25 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>754</v>
+        <v>726</v>
       </c>
       <c r="D603" t="n">
-        <v>763.25</v>
+        <v>770</v>
       </c>
       <c r="E603" t="n">
-        <v>743.35</v>
+        <v>725.15</v>
       </c>
       <c r="F603" t="n">
-        <v>756.4</v>
+        <v>763.75</v>
       </c>
       <c r="G603" t="n">
-        <v>1714771</v>
+        <v>3139171</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -35750,25 +35750,25 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="D604" t="n">
-        <v>783.35</v>
+        <v>759.6</v>
       </c>
       <c r="E604" t="n">
-        <v>752.15</v>
+        <v>736.05</v>
       </c>
       <c r="F604" t="n">
-        <v>765.5</v>
+        <v>747.3</v>
       </c>
       <c r="G604" t="n">
-        <v>1842284</v>
+        <v>1983807</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -35777,25 +35777,25 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D605" t="n">
-        <v>765.4</v>
+        <v>763.25</v>
       </c>
       <c r="E605" t="n">
-        <v>738.15</v>
+        <v>743.35</v>
       </c>
       <c r="F605" t="n">
-        <v>742</v>
+        <v>756.4</v>
       </c>
       <c r="G605" t="n">
-        <v>1289189</v>
+        <v>1714771</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -35804,25 +35804,25 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>743</v>
+        <v>760</v>
       </c>
       <c r="D606" t="n">
-        <v>763.5</v>
+        <v>783.35</v>
       </c>
       <c r="E606" t="n">
-        <v>737.1</v>
+        <v>752.15</v>
       </c>
       <c r="F606" t="n">
-        <v>751.55</v>
+        <v>765.5</v>
       </c>
       <c r="G606" t="n">
-        <v>1040836</v>
+        <v>1842284</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -35831,25 +35831,25 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>730.05</v>
+        <v>758</v>
       </c>
       <c r="D607" t="n">
-        <v>737.8</v>
+        <v>765.4</v>
       </c>
       <c r="E607" t="n">
-        <v>711.15</v>
+        <v>738.15</v>
       </c>
       <c r="F607" t="n">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="G607" t="n">
-        <v>2434320</v>
+        <v>1289189</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -35858,25 +35858,25 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>719</v>
+        <v>743</v>
       </c>
       <c r="D608" t="n">
-        <v>799</v>
+        <v>763.5</v>
       </c>
       <c r="E608" t="n">
-        <v>714</v>
+        <v>737.1</v>
       </c>
       <c r="F608" t="n">
-        <v>777.35</v>
+        <v>751.55</v>
       </c>
       <c r="G608" t="n">
-        <v>7602887</v>
+        <v>1040836</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -35885,25 +35885,25 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>783</v>
+        <v>730.05</v>
       </c>
       <c r="D609" t="n">
-        <v>801</v>
+        <v>737.8</v>
       </c>
       <c r="E609" t="n">
-        <v>770.15</v>
+        <v>711.15</v>
       </c>
       <c r="F609" t="n">
-        <v>786.05</v>
+        <v>722</v>
       </c>
       <c r="G609" t="n">
-        <v>2612869</v>
+        <v>2434320</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -35912,25 +35912,25 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>779.9</v>
+        <v>719</v>
       </c>
       <c r="D610" t="n">
-        <v>812.85</v>
+        <v>799</v>
       </c>
       <c r="E610" t="n">
-        <v>772.9</v>
+        <v>714</v>
       </c>
       <c r="F610" t="n">
-        <v>792.15</v>
+        <v>777.35</v>
       </c>
       <c r="G610" t="n">
-        <v>5370306</v>
+        <v>7602887</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -35939,25 +35939,25 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>792.15</v>
+        <v>783</v>
       </c>
       <c r="D611" t="n">
-        <v>792.15</v>
+        <v>801</v>
       </c>
       <c r="E611" t="n">
-        <v>792.15</v>
+        <v>770.15</v>
       </c>
       <c r="F611" t="n">
-        <v>792.15</v>
+        <v>786.05</v>
       </c>
       <c r="G611" t="n">
-        <v>0</v>
+        <v>2612869</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -35966,79 +35966,79 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>801</v>
+        <v>779.9</v>
       </c>
       <c r="D612" t="n">
-        <v>856.1</v>
+        <v>812.85</v>
       </c>
       <c r="E612" t="n">
-        <v>796</v>
+        <v>772.9</v>
       </c>
       <c r="F612" t="n">
-        <v>812.9</v>
+        <v>792.15</v>
       </c>
       <c r="G612" t="n">
-        <v>12561061</v>
+        <v>5370306</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>2175</v>
+        <v>792.15</v>
       </c>
       <c r="D613" t="n">
-        <v>2348.9</v>
+        <v>792.15</v>
       </c>
       <c r="E613" t="n">
-        <v>2133</v>
+        <v>792.15</v>
       </c>
       <c r="F613" t="n">
-        <v>2311.9</v>
+        <v>792.15</v>
       </c>
       <c r="G613" t="n">
-        <v>19963038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>2290</v>
+        <v>801</v>
       </c>
       <c r="D614" t="n">
-        <v>2422</v>
+        <v>856.1</v>
       </c>
       <c r="E614" t="n">
-        <v>2266.7</v>
+        <v>796</v>
       </c>
       <c r="F614" t="n">
-        <v>2409.2</v>
+        <v>812.9</v>
       </c>
       <c r="G614" t="n">
-        <v>6106908</v>
+        <v>12561061</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -36047,25 +36047,25 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>2394.1</v>
+        <v>2175</v>
       </c>
       <c r="D615" t="n">
-        <v>2433.9</v>
+        <v>2348.9</v>
       </c>
       <c r="E615" t="n">
-        <v>2301</v>
+        <v>2133</v>
       </c>
       <c r="F615" t="n">
-        <v>2345.5</v>
+        <v>2311.9</v>
       </c>
       <c r="G615" t="n">
-        <v>2480694</v>
+        <v>19963038</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -36074,25 +36074,25 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>2300</v>
+        <v>2290</v>
       </c>
       <c r="D616" t="n">
-        <v>2350</v>
+        <v>2422</v>
       </c>
       <c r="E616" t="n">
-        <v>2203.7</v>
+        <v>2266.7</v>
       </c>
       <c r="F616" t="n">
-        <v>2306.7</v>
+        <v>2409.2</v>
       </c>
       <c r="G616" t="n">
-        <v>5769711</v>
+        <v>6106908</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -36101,25 +36101,25 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>2315</v>
+        <v>2394.1</v>
       </c>
       <c r="D617" t="n">
-        <v>2437.3</v>
+        <v>2433.9</v>
       </c>
       <c r="E617" t="n">
-        <v>2313.7</v>
+        <v>2301</v>
       </c>
       <c r="F617" t="n">
-        <v>2405.8</v>
+        <v>2345.5</v>
       </c>
       <c r="G617" t="n">
-        <v>4076090</v>
+        <v>2480694</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -36128,25 +36128,25 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>2430</v>
+        <v>2300</v>
       </c>
       <c r="D618" t="n">
-        <v>2443.9</v>
+        <v>2350</v>
       </c>
       <c r="E618" t="n">
-        <v>2351</v>
+        <v>2203.7</v>
       </c>
       <c r="F618" t="n">
-        <v>2373.8</v>
+        <v>2306.7</v>
       </c>
       <c r="G618" t="n">
-        <v>1342665</v>
+        <v>5769711</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -36155,25 +36155,25 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>2350.5</v>
+        <v>2315</v>
       </c>
       <c r="D619" t="n">
-        <v>2425</v>
+        <v>2437.3</v>
       </c>
       <c r="E619" t="n">
-        <v>2328</v>
+        <v>2313.7</v>
       </c>
       <c r="F619" t="n">
-        <v>2391</v>
+        <v>2405.8</v>
       </c>
       <c r="G619" t="n">
-        <v>1286940</v>
+        <v>4076090</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -36182,25 +36182,25 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>2398</v>
+        <v>2430</v>
       </c>
       <c r="D620" t="n">
-        <v>2575</v>
+        <v>2443.9</v>
       </c>
       <c r="E620" t="n">
-        <v>2385</v>
+        <v>2351</v>
       </c>
       <c r="F620" t="n">
-        <v>2553.6</v>
+        <v>2373.8</v>
       </c>
       <c r="G620" t="n">
-        <v>3607692</v>
+        <v>1342665</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -36209,25 +36209,25 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>2561.6</v>
+        <v>2350.5</v>
       </c>
       <c r="D621" t="n">
-        <v>2592</v>
+        <v>2425</v>
       </c>
       <c r="E621" t="n">
-        <v>2510</v>
+        <v>2328</v>
       </c>
       <c r="F621" t="n">
-        <v>2523.5</v>
+        <v>2391</v>
       </c>
       <c r="G621" t="n">
-        <v>2258642</v>
+        <v>1286940</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -36236,25 +36236,25 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>2554.7</v>
+        <v>2398</v>
       </c>
       <c r="D622" t="n">
-        <v>2676</v>
+        <v>2575</v>
       </c>
       <c r="E622" t="n">
+        <v>2385</v>
+      </c>
+      <c r="F622" t="n">
         <v>2553.6</v>
       </c>
-      <c r="F622" t="n">
-        <v>2641.6</v>
-      </c>
       <c r="G622" t="n">
-        <v>4190711</v>
+        <v>3607692</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -36263,25 +36263,25 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>2649.2</v>
+        <v>2561.6</v>
       </c>
       <c r="D623" t="n">
-        <v>2662</v>
+        <v>2592</v>
       </c>
       <c r="E623" t="n">
-        <v>2566</v>
+        <v>2510</v>
       </c>
       <c r="F623" t="n">
-        <v>2590.6</v>
+        <v>2523.5</v>
       </c>
       <c r="G623" t="n">
-        <v>1247810</v>
+        <v>2258642</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -36290,25 +36290,25 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>2584.9</v>
+        <v>2554.7</v>
       </c>
       <c r="D624" t="n">
-        <v>2674.8</v>
+        <v>2676</v>
       </c>
       <c r="E624" t="n">
-        <v>2536.8</v>
+        <v>2553.6</v>
       </c>
       <c r="F624" t="n">
-        <v>2597.9</v>
+        <v>2641.6</v>
       </c>
       <c r="G624" t="n">
-        <v>1503451</v>
+        <v>4190711</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -36317,25 +36317,25 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>2611.1</v>
+        <v>2649.2</v>
       </c>
       <c r="D625" t="n">
-        <v>2641.7</v>
+        <v>2662</v>
       </c>
       <c r="E625" t="n">
-        <v>2575.5</v>
+        <v>2566</v>
       </c>
       <c r="F625" t="n">
-        <v>2599.5</v>
+        <v>2590.6</v>
       </c>
       <c r="G625" t="n">
-        <v>1053885</v>
+        <v>1247810</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -36344,25 +36344,25 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>2602.9</v>
+        <v>2584.9</v>
       </c>
       <c r="D626" t="n">
-        <v>2652</v>
+        <v>2674.8</v>
       </c>
       <c r="E626" t="n">
-        <v>2586.1</v>
+        <v>2536.8</v>
       </c>
       <c r="F626" t="n">
-        <v>2608.5</v>
+        <v>2597.9</v>
       </c>
       <c r="G626" t="n">
-        <v>759849</v>
+        <v>1503451</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -36371,25 +36371,25 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>2614</v>
+        <v>2611.1</v>
       </c>
       <c r="D627" t="n">
-        <v>2784.8</v>
+        <v>2641.7</v>
       </c>
       <c r="E627" t="n">
-        <v>2606.5</v>
+        <v>2575.5</v>
       </c>
       <c r="F627" t="n">
-        <v>2776.9</v>
+        <v>2599.5</v>
       </c>
       <c r="G627" t="n">
-        <v>4261554</v>
+        <v>1053885</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -36398,25 +36398,25 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>2745</v>
+        <v>2602.9</v>
       </c>
       <c r="D628" t="n">
-        <v>2761.8</v>
+        <v>2652</v>
       </c>
       <c r="E628" t="n">
-        <v>2658.5</v>
+        <v>2586.1</v>
       </c>
       <c r="F628" t="n">
-        <v>2676.6</v>
+        <v>2608.5</v>
       </c>
       <c r="G628" t="n">
-        <v>1221515</v>
+        <v>759849</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -36425,25 +36425,25 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>2676.6</v>
+        <v>2614</v>
       </c>
       <c r="D629" t="n">
-        <v>2676.6</v>
+        <v>2784.8</v>
       </c>
       <c r="E629" t="n">
-        <v>2676.6</v>
+        <v>2606.5</v>
       </c>
       <c r="F629" t="n">
-        <v>2676.6</v>
+        <v>2776.9</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>4261554</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -36452,25 +36452,25 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>2661.2</v>
+        <v>2745</v>
       </c>
       <c r="D630" t="n">
-        <v>2718.4</v>
+        <v>2761.8</v>
       </c>
       <c r="E630" t="n">
-        <v>2363.6</v>
+        <v>2658.5</v>
       </c>
       <c r="F630" t="n">
-        <v>2413.3</v>
+        <v>2676.6</v>
       </c>
       <c r="G630" t="n">
-        <v>3340619</v>
+        <v>1221515</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -36479,25 +36479,25 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>2413</v>
+        <v>2676.6</v>
       </c>
       <c r="D631" t="n">
-        <v>2448.7</v>
+        <v>2676.6</v>
       </c>
       <c r="E631" t="n">
-        <v>2240.2</v>
+        <v>2676.6</v>
       </c>
       <c r="F631" t="n">
-        <v>2424.5</v>
+        <v>2676.6</v>
       </c>
       <c r="G631" t="n">
-        <v>2931474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -36506,25 +36506,25 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>2420</v>
+        <v>2661.2</v>
       </c>
       <c r="D632" t="n">
-        <v>2508</v>
+        <v>2718.4</v>
       </c>
       <c r="E632" t="n">
-        <v>2415.1</v>
+        <v>2363.6</v>
       </c>
       <c r="F632" t="n">
-        <v>2460.3</v>
+        <v>2413.3</v>
       </c>
       <c r="G632" t="n">
-        <v>1698993</v>
+        <v>3340619</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -36533,25 +36533,25 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>2472.6</v>
+        <v>2413</v>
       </c>
       <c r="D633" t="n">
-        <v>2678.7</v>
+        <v>2448.7</v>
       </c>
       <c r="E633" t="n">
-        <v>2472.6</v>
+        <v>2240.2</v>
       </c>
       <c r="F633" t="n">
-        <v>2660.1</v>
+        <v>2424.5</v>
       </c>
       <c r="G633" t="n">
-        <v>4629365</v>
+        <v>2931474</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -36560,25 +36560,25 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>2758</v>
+        <v>2420</v>
       </c>
       <c r="D634" t="n">
-        <v>2797.6</v>
+        <v>2508</v>
       </c>
       <c r="E634" t="n">
-        <v>2666.2</v>
+        <v>2415.1</v>
       </c>
       <c r="F634" t="n">
-        <v>2762.7</v>
+        <v>2460.3</v>
       </c>
       <c r="G634" t="n">
-        <v>2544698</v>
+        <v>1698993</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -36587,25 +36587,25 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>2762.7</v>
+        <v>2472.6</v>
       </c>
       <c r="D635" t="n">
-        <v>2829</v>
+        <v>2678.7</v>
       </c>
       <c r="E635" t="n">
-        <v>2706.7</v>
+        <v>2472.6</v>
       </c>
       <c r="F635" t="n">
-        <v>2731.5</v>
+        <v>2660.1</v>
       </c>
       <c r="G635" t="n">
-        <v>1437944</v>
+        <v>4629365</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -36614,25 +36614,25 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>2740.5</v>
+        <v>2758</v>
       </c>
       <c r="D636" t="n">
-        <v>2836</v>
+        <v>2797.6</v>
       </c>
       <c r="E636" t="n">
-        <v>2736</v>
+        <v>2666.2</v>
       </c>
       <c r="F636" t="n">
-        <v>2796.8</v>
+        <v>2762.7</v>
       </c>
       <c r="G636" t="n">
-        <v>1740034</v>
+        <v>2544698</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -36641,25 +36641,25 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>2786</v>
+        <v>2762.7</v>
       </c>
       <c r="D637" t="n">
-        <v>2800</v>
+        <v>2829</v>
       </c>
       <c r="E637" t="n">
-        <v>2675</v>
+        <v>2706.7</v>
       </c>
       <c r="F637" t="n">
-        <v>2692.2</v>
+        <v>2731.5</v>
       </c>
       <c r="G637" t="n">
-        <v>1002471</v>
+        <v>1437944</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -36668,25 +36668,25 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>2752.9</v>
+        <v>2740.5</v>
       </c>
       <c r="D638" t="n">
-        <v>2837.5</v>
+        <v>2836</v>
       </c>
       <c r="E638" t="n">
-        <v>2752.9</v>
+        <v>2736</v>
       </c>
       <c r="F638" t="n">
-        <v>2832.4</v>
+        <v>2796.8</v>
       </c>
       <c r="G638" t="n">
-        <v>2763523</v>
+        <v>1740034</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -36695,25 +36695,25 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>2830</v>
+        <v>2786</v>
       </c>
       <c r="D639" t="n">
-        <v>2838</v>
+        <v>2800</v>
       </c>
       <c r="E639" t="n">
-        <v>2684.5</v>
+        <v>2675</v>
       </c>
       <c r="F639" t="n">
-        <v>2739.7</v>
+        <v>2692.2</v>
       </c>
       <c r="G639" t="n">
-        <v>1348785</v>
+        <v>1002471</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -36722,25 +36722,25 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>2712.3</v>
+        <v>2752.9</v>
       </c>
       <c r="D640" t="n">
-        <v>2900</v>
+        <v>2837.5</v>
       </c>
       <c r="E640" t="n">
-        <v>2680.5</v>
+        <v>2752.9</v>
       </c>
       <c r="F640" t="n">
-        <v>2842</v>
+        <v>2832.4</v>
       </c>
       <c r="G640" t="n">
-        <v>3094471</v>
+        <v>2763523</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -36749,25 +36749,25 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>2802</v>
+        <v>2830</v>
       </c>
       <c r="D641" t="n">
-        <v>2835.8</v>
+        <v>2838</v>
       </c>
       <c r="E641" t="n">
-        <v>2700.9</v>
+        <v>2684.5</v>
       </c>
       <c r="F641" t="n">
-        <v>2717</v>
+        <v>2739.7</v>
       </c>
       <c r="G641" t="n">
-        <v>1718055</v>
+        <v>1348785</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -36776,25 +36776,25 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>2708</v>
+        <v>2712.3</v>
       </c>
       <c r="D642" t="n">
-        <v>2731.3</v>
+        <v>2900</v>
       </c>
       <c r="E642" t="n">
-        <v>2539.2</v>
+        <v>2680.5</v>
       </c>
       <c r="F642" t="n">
-        <v>2605.8</v>
+        <v>2842</v>
       </c>
       <c r="G642" t="n">
-        <v>2309126</v>
+        <v>3094471</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -36803,45 +36803,99 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>2605.8</v>
+        <v>2802</v>
       </c>
       <c r="D643" t="n">
-        <v>2605.8</v>
+        <v>2835.8</v>
       </c>
       <c r="E643" t="n">
-        <v>2605.8</v>
+        <v>2700.9</v>
       </c>
       <c r="F643" t="n">
-        <v>2605.8</v>
+        <v>2717</v>
       </c>
       <c r="G643" t="n">
-        <v>0</v>
+        <v>1718055</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>2708</v>
+      </c>
+      <c r="D644" t="n">
+        <v>2731.3</v>
+      </c>
+      <c r="E644" t="n">
+        <v>2539.2</v>
+      </c>
+      <c r="F644" t="n">
+        <v>2605.8</v>
+      </c>
+      <c r="G644" t="n">
+        <v>2309126</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2605.8</v>
+      </c>
+      <c r="D645" t="n">
+        <v>2605.8</v>
+      </c>
+      <c r="E645" t="n">
+        <v>2605.8</v>
+      </c>
+      <c r="F645" t="n">
+        <v>2605.8</v>
+      </c>
+      <c r="G645" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C644" t="n">
+      <c r="C646" t="n">
         <v>2649.9</v>
       </c>
-      <c r="D644" t="n">
+      <c r="D646" t="n">
         <v>2672.9</v>
       </c>
-      <c r="E644" t="n">
+      <c r="E646" t="n">
         <v>2450</v>
       </c>
-      <c r="F644" t="n">
+      <c r="F646" t="n">
         <v>2497.5</v>
       </c>
-      <c r="G644" t="n">
+      <c r="G646" t="n">
         <v>2352647</v>
       </c>
     </row>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 20 Oct 2026 21:47</t>
+          <t>Generated 21 Oct 2026 21:53</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9507,6 +9507,192 @@
         <v>1</v>
       </c>
       <c r="P142" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100</v>
+      </c>
+      <c r="F143" t="n">
+        <v>466.78</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K143" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="L143" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="M143" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="O143" t="b">
+        <v>1</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>98</v>
+      </c>
+      <c r="F144" t="n">
+        <v>191.01</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>2592.9</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2313.39</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-10.78</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2872.41</v>
+      </c>
+      <c r="L144" t="n">
+        <v>3151.92</v>
+      </c>
+      <c r="M144" t="n">
+        <v>279.51</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O144" t="b">
+        <v>1</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>92</v>
+      </c>
+      <c r="F145" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>2069</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1970.1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="K145" t="n">
+        <v>2167.9</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2266.8</v>
+      </c>
+      <c r="M145" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="O145" t="b">
+        <v>1</v>
+      </c>
+      <c r="P145" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -9523,7 +9709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14163,6 +14349,105 @@
         <v>2167.9</v>
       </c>
       <c r="I142" t="n">
+        <v>2266.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="E143" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="H143" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="I143" t="n">
+        <v>400.2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2592.9</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2313.39</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-10.78</v>
+      </c>
+      <c r="G144" t="n">
+        <v>279.51</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2872.41</v>
+      </c>
+      <c r="I144" t="n">
+        <v>3151.92</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2069</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1970.1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="G145" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2167.9</v>
+      </c>
+      <c r="I145" t="n">
         <v>2266.8</v>
       </c>
     </row>
@@ -44338,7 +44623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45063,6 +45348,21 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
